--- a/stored_files/templates/DAINESE/DAINESE_NHAP_SEA_AIR_template.xlsx
+++ b/stored_files/templates/DAINESE/DAINESE_NHAP_SEA_AIR_template.xlsx
@@ -1526,12 +1526,6 @@
         <t xml:space="preserve">Hi:
 KBHC
 </t>
-      </text>
-    </comment>
-    <comment ref="R27" authorId="0" shapeId="0">
-      <text>
-        <t>Hi:
-xlhh&amp; lưu kho</t>
       </text>
     </comment>
   </commentList>
@@ -1889,7 +1883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HT203"/>
+  <dimension ref="A1:HT188"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.08984375" defaultRowHeight="15.5"/>
   <cols>
     <col width="5.36328125" customWidth="1" style="16" min="1" max="1"/>
@@ -2351,1722 +2345,1067 @@
       </c>
     </row>
     <row r="14" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A14" s="74" t="n"/>
-      <c r="B14" s="75" t="n"/>
-      <c r="C14" s="75" t="n"/>
-      <c r="D14" s="76" t="n"/>
-      <c r="E14" s="77" t="n"/>
-      <c r="F14" s="76" t="n"/>
-      <c r="G14" s="76" t="n"/>
-      <c r="H14" s="76" t="n"/>
-      <c r="I14" s="76" t="n"/>
-      <c r="J14" s="76" t="n"/>
-      <c r="K14" s="79" t="n"/>
-      <c r="L14" s="150" t="n"/>
-      <c r="M14" s="79" t="n"/>
-      <c r="N14" s="79" t="n"/>
-      <c r="O14" s="79" t="n"/>
-      <c r="P14" s="79" t="n"/>
-      <c r="Q14" s="79" t="n"/>
-      <c r="R14" s="79" t="n"/>
-      <c r="S14" s="79" t="n"/>
-      <c r="T14" s="79" t="n"/>
-      <c r="U14" s="150" t="n"/>
-      <c r="V14" s="150">
-        <f>SUM(K14:U14)</f>
+      <c r="A14" s="98" t="n"/>
+      <c r="B14" s="141" t="n"/>
+      <c r="C14" s="141" t="n"/>
+      <c r="D14" s="141" t="n"/>
+      <c r="E14" s="141" t="n"/>
+      <c r="F14" s="141" t="n"/>
+      <c r="G14" s="141" t="n"/>
+      <c r="H14" s="141" t="n"/>
+      <c r="I14" s="141" t="n"/>
+      <c r="J14" s="142" t="n"/>
+      <c r="K14" s="64">
+        <f>SUM(K13:K13)</f>
         <v/>
       </c>
-      <c r="W14" s="150" t="n"/>
-      <c r="X14" s="79" t="n"/>
-      <c r="Y14" s="79">
-        <f>1153600+44550</f>
+      <c r="L14" s="64">
+        <f>SUM(L13:L13)</f>
         <v/>
       </c>
-      <c r="Z14" s="150">
-        <f>SUM(W14:Y14)</f>
+      <c r="M14" s="64">
+        <f>SUM(M13:M13)</f>
         <v/>
       </c>
-      <c r="AA14" s="151">
-        <f>+V14+Z14</f>
+      <c r="N14" s="64">
+        <f>SUM(N13:N13)</f>
         <v/>
       </c>
-      <c r="AB14" s="138" t="inlineStr">
-        <is>
-          <t>2915, 2934</t>
-        </is>
-      </c>
-      <c r="AC14" s="71" t="n">
-        <v>149</v>
-      </c>
-      <c r="AD14" s="72" t="n">
-        <v>185</v>
-      </c>
+      <c r="O14" s="64">
+        <f>SUM(O13:O13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="64">
+        <f>SUM(P13:P13)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="64">
+        <f>SUM(Q13:Q13)</f>
+        <v/>
+      </c>
+      <c r="R14" s="64">
+        <f>SUM(R13:R13)</f>
+        <v/>
+      </c>
+      <c r="S14" s="64">
+        <f>SUM(S13:S13)</f>
+        <v/>
+      </c>
+      <c r="T14" s="64">
+        <f>SUM(T13:T13)</f>
+        <v/>
+      </c>
+      <c r="U14" s="64">
+        <f>SUM(U13:U13)</f>
+        <v/>
+      </c>
+      <c r="V14" s="64">
+        <f>SUM(V13:V13)</f>
+        <v/>
+      </c>
+      <c r="W14" s="64">
+        <f>SUM(W13:W13)</f>
+        <v/>
+      </c>
+      <c r="X14" s="64">
+        <f>SUM(X13:X13)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="64">
+        <f>SUM(Y13:Y13)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="64">
+        <f>SUM(Z13:Z13)</f>
+        <v/>
+      </c>
+      <c r="AA14" s="65">
+        <f>SUM(AA13:AA13)</f>
+        <v/>
+      </c>
+      <c r="AB14" s="56" t="n"/>
+      <c r="AC14" s="50" t="n"/>
+      <c r="AD14" s="50" t="n"/>
     </row>
     <row r="15" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A15" s="74" t="n"/>
-      <c r="B15" s="75" t="n"/>
-      <c r="C15" s="75" t="n"/>
-      <c r="D15" s="76" t="n"/>
-      <c r="E15" s="77" t="n"/>
-      <c r="F15" s="76" t="n"/>
-      <c r="G15" s="76" t="n"/>
-      <c r="H15" s="76" t="n"/>
-      <c r="I15" s="76" t="n"/>
-      <c r="J15" s="76" t="n"/>
-      <c r="K15" s="79" t="n"/>
-      <c r="L15" s="150" t="n"/>
-      <c r="M15" s="79" t="n"/>
-      <c r="N15" s="79" t="n"/>
-      <c r="O15" s="79" t="n"/>
-      <c r="P15" s="79" t="n"/>
-      <c r="Q15" s="79" t="n"/>
-      <c r="R15" s="79" t="n"/>
-      <c r="S15" s="79" t="n"/>
-      <c r="T15" s="79" t="n"/>
-      <c r="U15" s="150" t="n"/>
-      <c r="V15" s="150">
-        <f>SUM(K15:U15)</f>
+      <c r="A15" s="100" t="n"/>
+      <c r="B15" s="154" t="n"/>
+      <c r="C15" s="154" t="n"/>
+      <c r="D15" s="154" t="n"/>
+      <c r="E15" s="154" t="n"/>
+      <c r="F15" s="154" t="n"/>
+      <c r="G15" s="154" t="n"/>
+      <c r="H15" s="154" t="n"/>
+      <c r="I15" s="154" t="n"/>
+      <c r="J15" s="155" t="n"/>
+      <c r="K15" s="27" t="n"/>
+      <c r="L15" s="27" t="n"/>
+      <c r="M15" s="27" t="n"/>
+      <c r="N15" s="27" t="n"/>
+      <c r="O15" s="27" t="n"/>
+      <c r="P15" s="27" t="n"/>
+      <c r="Q15" s="27" t="n"/>
+      <c r="R15" s="27" t="n"/>
+      <c r="S15" s="27" t="n"/>
+      <c r="T15" s="27" t="n"/>
+      <c r="U15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="52" t="n"/>
+      <c r="AC15" s="23" t="n"/>
+      <c r="AD15" s="23" t="n"/>
+    </row>
+    <row r="16" ht="37" customFormat="1" customHeight="1" s="59">
+      <c r="A16" s="102" t="n"/>
+      <c r="B16" s="156" t="n"/>
+      <c r="C16" s="156" t="n"/>
+      <c r="D16" s="156" t="n"/>
+      <c r="E16" s="156" t="n"/>
+      <c r="F16" s="156" t="n"/>
+      <c r="G16" s="156" t="n"/>
+      <c r="H16" s="156" t="n"/>
+      <c r="I16" s="156" t="n"/>
+      <c r="J16" s="157" t="n"/>
+      <c r="K16" s="13">
+        <f>SUM(K14:K15)</f>
         <v/>
       </c>
-      <c r="W15" s="150" t="n"/>
-      <c r="X15" s="79" t="n"/>
-      <c r="Y15" s="79" t="n">
-        <v>685800</v>
-      </c>
-      <c r="Z15" s="150">
-        <f>SUM(W15:Y15)</f>
+      <c r="L16" s="13">
+        <f>SUM(L14:L15)</f>
         <v/>
       </c>
-      <c r="AA15" s="151">
-        <f>+V15+Z15</f>
+      <c r="M16" s="13">
+        <f>SUM(M14:M15)</f>
         <v/>
       </c>
-      <c r="AB15" s="138" t="inlineStr">
-        <is>
-          <t>9512</t>
-        </is>
-      </c>
-      <c r="AC15" s="71" t="n">
-        <v>148</v>
-      </c>
-      <c r="AD15" s="72" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="16" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A16" s="74" t="n"/>
-      <c r="B16" s="75" t="n"/>
-      <c r="C16" s="75" t="n"/>
-      <c r="D16" s="76" t="n"/>
-      <c r="E16" s="77" t="n"/>
-      <c r="F16" s="76" t="n"/>
-      <c r="G16" s="76" t="n"/>
-      <c r="H16" s="76" t="n"/>
-      <c r="I16" s="76" t="n"/>
-      <c r="J16" s="76" t="n"/>
-      <c r="K16" s="79" t="n"/>
-      <c r="L16" s="150" t="n"/>
-      <c r="M16" s="79" t="n"/>
-      <c r="N16" s="79" t="n"/>
-      <c r="O16" s="79" t="n"/>
-      <c r="P16" s="79" t="n"/>
-      <c r="Q16" s="79" t="n"/>
-      <c r="R16" s="79" t="n"/>
-      <c r="S16" s="79" t="n"/>
-      <c r="T16" s="79" t="n"/>
-      <c r="U16" s="150" t="n"/>
-      <c r="V16" s="150">
-        <f>SUM(K16:U16)</f>
+      <c r="N16" s="13">
+        <f>SUM(N14:N15)</f>
         <v/>
       </c>
-      <c r="W16" s="150" t="n"/>
-      <c r="X16" s="79" t="n">
-        <v>17920</v>
-      </c>
-      <c r="Y16" s="79" t="n">
-        <v>6175047</v>
-      </c>
-      <c r="Z16" s="150">
-        <f>SUM(W16:Y16)</f>
+      <c r="O16" s="13">
+        <f>SUM(O14:O15)</f>
         <v/>
       </c>
-      <c r="AA16" s="151">
-        <f>+V16+Z16</f>
+      <c r="P16" s="13">
+        <f>SUM(P14:P15)</f>
         <v/>
       </c>
-      <c r="AB16" s="138" t="inlineStr">
-        <is>
-          <t>18144, 1148969</t>
-        </is>
-      </c>
-      <c r="AC16" s="71" t="n">
-        <v>153</v>
-      </c>
-      <c r="AD16" s="72" t="n">
-        <v>187</v>
-      </c>
+      <c r="Q16" s="13">
+        <f>SUM(Q14:Q15)</f>
+        <v/>
+      </c>
+      <c r="R16" s="13">
+        <f>SUM(R14:R15)</f>
+        <v/>
+      </c>
+      <c r="S16" s="13">
+        <f>SUM(S14:S15)</f>
+        <v/>
+      </c>
+      <c r="T16" s="13">
+        <f>SUM(T14:T15)</f>
+        <v/>
+      </c>
+      <c r="U16" s="13">
+        <f>SUM(U14:U15)</f>
+        <v/>
+      </c>
+      <c r="V16" s="13">
+        <f>SUM(V14:V15)</f>
+        <v/>
+      </c>
+      <c r="W16" s="13">
+        <f>SUM(W14:W15)</f>
+        <v/>
+      </c>
+      <c r="X16" s="13">
+        <f>SUM(X14:X15)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="13">
+        <f>SUM(Y14:Y15)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="13">
+        <f>SUM(Z14:Z15)</f>
+        <v/>
+      </c>
+      <c r="AA16" s="47">
+        <f>SUM(AA14:AA15)</f>
+        <v/>
+      </c>
+      <c r="AB16" s="49" t="n"/>
+      <c r="AC16" s="50" t="n"/>
+      <c r="AD16" s="50" t="n"/>
+      <c r="AE16" s="50" t="n"/>
+      <c r="AF16" s="50" t="n"/>
+      <c r="AG16" s="50" t="n"/>
+      <c r="AH16" s="50" t="n"/>
+      <c r="AI16" s="50" t="n"/>
+      <c r="AJ16" s="50" t="n"/>
+      <c r="AK16" s="50" t="n"/>
+      <c r="AL16" s="50" t="n"/>
+      <c r="AM16" s="50" t="n"/>
+      <c r="AN16" s="50" t="n"/>
+      <c r="AO16" s="50" t="n"/>
+      <c r="AP16" s="50" t="n"/>
+      <c r="AQ16" s="50" t="n"/>
+      <c r="AR16" s="50" t="n"/>
+      <c r="AS16" s="50" t="n"/>
+      <c r="AT16" s="50" t="n"/>
+      <c r="AU16" s="50" t="n"/>
+      <c r="AV16" s="50" t="n"/>
+      <c r="AW16" s="50" t="n"/>
+      <c r="AX16" s="50" t="n"/>
+      <c r="AY16" s="50" t="n"/>
+      <c r="AZ16" s="50" t="n"/>
+      <c r="BA16" s="50" t="n"/>
+      <c r="BB16" s="50" t="n"/>
+      <c r="BC16" s="50" t="n"/>
+      <c r="BD16" s="50" t="n"/>
+      <c r="BE16" s="50" t="n"/>
+      <c r="BF16" s="50" t="n"/>
+      <c r="BG16" s="50" t="n"/>
+      <c r="BH16" s="50" t="n"/>
+      <c r="BI16" s="50" t="n"/>
+      <c r="BJ16" s="50" t="n"/>
+      <c r="BK16" s="50" t="n"/>
+      <c r="BL16" s="50" t="n"/>
+      <c r="BM16" s="50" t="n"/>
+      <c r="BN16" s="50" t="n"/>
+      <c r="BO16" s="50" t="n"/>
+      <c r="BP16" s="50" t="n"/>
+      <c r="BQ16" s="50" t="n"/>
+      <c r="BR16" s="50" t="n"/>
+      <c r="BS16" s="50" t="n"/>
+      <c r="BT16" s="50" t="n"/>
+      <c r="BU16" s="50" t="n"/>
+      <c r="BV16" s="50" t="n"/>
+      <c r="BW16" s="50" t="n"/>
+      <c r="BX16" s="50" t="n"/>
+      <c r="BY16" s="50" t="n"/>
+      <c r="BZ16" s="50" t="n"/>
+      <c r="CA16" s="50" t="n"/>
+      <c r="CB16" s="50" t="n"/>
+      <c r="CC16" s="50" t="n"/>
+      <c r="CD16" s="50" t="n"/>
+      <c r="CE16" s="50" t="n"/>
+      <c r="CF16" s="50" t="n"/>
+      <c r="CG16" s="50" t="n"/>
+      <c r="CH16" s="50" t="n"/>
+      <c r="CI16" s="50" t="n"/>
+      <c r="CJ16" s="50" t="n"/>
+      <c r="CK16" s="50" t="n"/>
+      <c r="CL16" s="50" t="n"/>
+      <c r="CM16" s="50" t="n"/>
+      <c r="CN16" s="50" t="n"/>
+      <c r="CO16" s="50" t="n"/>
+      <c r="CP16" s="50" t="n"/>
+      <c r="CQ16" s="50" t="n"/>
+      <c r="CR16" s="50" t="n"/>
+      <c r="CS16" s="50" t="n"/>
+      <c r="CT16" s="50" t="n"/>
+      <c r="CU16" s="50" t="n"/>
+      <c r="CV16" s="50" t="n"/>
+      <c r="CW16" s="50" t="n"/>
+      <c r="CX16" s="50" t="n"/>
+      <c r="CY16" s="50" t="n"/>
+      <c r="CZ16" s="50" t="n"/>
+      <c r="DA16" s="50" t="n"/>
+      <c r="DB16" s="50" t="n"/>
+      <c r="DC16" s="50" t="n"/>
+      <c r="DD16" s="50" t="n"/>
+      <c r="DE16" s="50" t="n"/>
+      <c r="DF16" s="50" t="n"/>
+      <c r="DG16" s="50" t="n"/>
+      <c r="DH16" s="50" t="n"/>
+      <c r="DI16" s="50" t="n"/>
+      <c r="DJ16" s="50" t="n"/>
+      <c r="DK16" s="50" t="n"/>
+      <c r="DL16" s="50" t="n"/>
+      <c r="DM16" s="50" t="n"/>
+      <c r="DN16" s="50" t="n"/>
+      <c r="DO16" s="50" t="n"/>
+      <c r="DP16" s="50" t="n"/>
+      <c r="DQ16" s="50" t="n"/>
+      <c r="DR16" s="50" t="n"/>
+      <c r="DS16" s="50" t="n"/>
+      <c r="DT16" s="50" t="n"/>
+      <c r="DU16" s="50" t="n"/>
+      <c r="DV16" s="50" t="n"/>
+      <c r="DW16" s="50" t="n"/>
+      <c r="DX16" s="50" t="n"/>
+      <c r="DY16" s="50" t="n"/>
+      <c r="DZ16" s="50" t="n"/>
+      <c r="EA16" s="50" t="n"/>
+      <c r="EB16" s="50" t="n"/>
+      <c r="EC16" s="50" t="n"/>
+      <c r="ED16" s="50" t="n"/>
+      <c r="EE16" s="50" t="n"/>
+      <c r="EF16" s="50" t="n"/>
+      <c r="EG16" s="50" t="n"/>
+      <c r="EH16" s="50" t="n"/>
+      <c r="EI16" s="50" t="n"/>
+      <c r="EJ16" s="50" t="n"/>
+      <c r="EK16" s="50" t="n"/>
+      <c r="EL16" s="50" t="n"/>
+      <c r="EM16" s="50" t="n"/>
+      <c r="EN16" s="50" t="n"/>
+      <c r="EO16" s="50" t="n"/>
+      <c r="EP16" s="50" t="n"/>
+      <c r="EQ16" s="50" t="n"/>
+      <c r="ER16" s="50" t="n"/>
+      <c r="ES16" s="50" t="n"/>
+      <c r="ET16" s="50" t="n"/>
+      <c r="EU16" s="50" t="n"/>
+      <c r="EV16" s="50" t="n"/>
+      <c r="EW16" s="50" t="n"/>
+      <c r="EX16" s="50" t="n"/>
+      <c r="EY16" s="50" t="n"/>
+      <c r="EZ16" s="50" t="n"/>
+      <c r="FA16" s="50" t="n"/>
+      <c r="FB16" s="50" t="n"/>
+      <c r="FC16" s="50" t="n"/>
+      <c r="FD16" s="50" t="n"/>
+      <c r="FE16" s="50" t="n"/>
+      <c r="FF16" s="50" t="n"/>
+      <c r="FG16" s="50" t="n"/>
+      <c r="FH16" s="50" t="n"/>
+      <c r="FI16" s="50" t="n"/>
+      <c r="FJ16" s="50" t="n"/>
+      <c r="FK16" s="50" t="n"/>
+      <c r="FL16" s="50" t="n"/>
+      <c r="FM16" s="50" t="n"/>
+      <c r="FN16" s="50" t="n"/>
+      <c r="FO16" s="50" t="n"/>
+      <c r="FP16" s="50" t="n"/>
+      <c r="FQ16" s="50" t="n"/>
+      <c r="FR16" s="50" t="n"/>
+      <c r="FS16" s="50" t="n"/>
+      <c r="FT16" s="50" t="n"/>
+      <c r="FU16" s="50" t="n"/>
+      <c r="FV16" s="50" t="n"/>
+      <c r="FW16" s="50" t="n"/>
+      <c r="FX16" s="50" t="n"/>
+      <c r="FY16" s="50" t="n"/>
+      <c r="FZ16" s="50" t="n"/>
+      <c r="GA16" s="50" t="n"/>
+      <c r="GB16" s="50" t="n"/>
+      <c r="GC16" s="50" t="n"/>
+      <c r="GD16" s="50" t="n"/>
+      <c r="GE16" s="50" t="n"/>
+      <c r="GF16" s="50" t="n"/>
+      <c r="GG16" s="50" t="n"/>
+      <c r="GH16" s="50" t="n"/>
+      <c r="GI16" s="50" t="n"/>
+      <c r="GJ16" s="50" t="n"/>
+      <c r="GK16" s="50" t="n"/>
+      <c r="GL16" s="50" t="n"/>
+      <c r="GM16" s="50" t="n"/>
+      <c r="GN16" s="50" t="n"/>
+      <c r="GO16" s="50" t="n"/>
+      <c r="GP16" s="50" t="n"/>
+      <c r="GQ16" s="50" t="n"/>
+      <c r="GR16" s="50" t="n"/>
+      <c r="GS16" s="50" t="n"/>
+      <c r="GT16" s="50" t="n"/>
+      <c r="GU16" s="50" t="n"/>
+      <c r="GV16" s="50" t="n"/>
+      <c r="GW16" s="50" t="n"/>
+      <c r="GX16" s="50" t="n"/>
+      <c r="GY16" s="50" t="n"/>
+      <c r="GZ16" s="50" t="n"/>
+      <c r="HA16" s="50" t="n"/>
+      <c r="HB16" s="50" t="n"/>
+      <c r="HC16" s="50" t="n"/>
+      <c r="HD16" s="50" t="n"/>
+      <c r="HE16" s="50" t="n"/>
+      <c r="HF16" s="50" t="n"/>
+      <c r="HG16" s="50" t="n"/>
+      <c r="HH16" s="50" t="n"/>
+      <c r="HI16" s="50" t="n"/>
+      <c r="HJ16" s="50" t="n"/>
+      <c r="HK16" s="50" t="n"/>
+      <c r="HL16" s="50" t="n"/>
+      <c r="HM16" s="50" t="n"/>
+      <c r="HN16" s="50" t="n"/>
+      <c r="HO16" s="50" t="n"/>
+      <c r="HP16" s="50" t="n"/>
+      <c r="HQ16" s="50" t="n"/>
+      <c r="HR16" s="50" t="n"/>
+      <c r="HS16" s="50" t="n"/>
+      <c r="HT16" s="50" t="n"/>
     </row>
     <row r="17" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A17" s="74" t="n"/>
-      <c r="B17" s="75" t="n"/>
-      <c r="C17" s="75" t="n"/>
-      <c r="D17" s="76" t="n"/>
-      <c r="E17" s="77" t="n"/>
-      <c r="F17" s="76" t="n"/>
-      <c r="G17" s="76" t="n"/>
-      <c r="H17" s="76" t="n"/>
-      <c r="I17" s="76" t="n"/>
-      <c r="J17" s="76" t="n"/>
-      <c r="K17" s="79" t="n"/>
-      <c r="L17" s="150" t="n"/>
-      <c r="M17" s="79" t="n"/>
-      <c r="N17" s="79" t="n"/>
-      <c r="O17" s="79" t="n"/>
-      <c r="P17" s="79" t="n"/>
-      <c r="Q17" s="79" t="n"/>
-      <c r="R17" s="79" t="n"/>
-      <c r="S17" s="79" t="n"/>
-      <c r="T17" s="79" t="n"/>
-      <c r="U17" s="150" t="n"/>
-      <c r="V17" s="150">
-        <f>SUM(K17:U17)</f>
-        <v/>
-      </c>
-      <c r="W17" s="150" t="n">
-        <v>3150575</v>
-      </c>
-      <c r="X17" s="79" t="n"/>
-      <c r="Y17" s="79" t="n">
-        <v>3864240</v>
-      </c>
-      <c r="Z17" s="150">
-        <f>SUM(W17:Y17)</f>
-        <v/>
-      </c>
-      <c r="AA17" s="151">
-        <f>+V17+Z17</f>
-        <v/>
-      </c>
-      <c r="AB17" s="138" t="inlineStr">
-        <is>
-          <t>4200</t>
-        </is>
-      </c>
-      <c r="AC17" s="71" t="n">
-        <v>157</v>
-      </c>
-      <c r="AD17" s="72" t="n">
-        <v>188</v>
-      </c>
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="88" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="18" t="n"/>
+      <c r="L17" s="18" t="n"/>
+      <c r="M17" s="18" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
+      <c r="R17" s="16" t="n"/>
+      <c r="S17" s="16" t="n"/>
+      <c r="T17" s="16" t="n"/>
+      <c r="U17" s="16" t="n"/>
+      <c r="V17" s="16" t="n"/>
+      <c r="W17" s="16" t="n"/>
+      <c r="X17" s="16" t="n"/>
+      <c r="Y17" s="16" t="n"/>
+      <c r="Z17" s="16" t="n"/>
+      <c r="AA17" s="16" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="16" t="n"/>
+      <c r="AD17" s="16" t="n"/>
     </row>
     <row r="18" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A18" s="74" t="n"/>
-      <c r="B18" s="75" t="n"/>
-      <c r="C18" s="75" t="n"/>
-      <c r="D18" s="76" t="n"/>
-      <c r="E18" s="77" t="n"/>
-      <c r="F18" s="76" t="n"/>
-      <c r="G18" s="76" t="n"/>
-      <c r="H18" s="76" t="n"/>
-      <c r="I18" s="76" t="n"/>
-      <c r="J18" s="76" t="n"/>
-      <c r="K18" s="79" t="n"/>
-      <c r="L18" s="150" t="n"/>
-      <c r="M18" s="79" t="n"/>
-      <c r="N18" s="79" t="n"/>
-      <c r="O18" s="79" t="n"/>
-      <c r="P18" s="79" t="n"/>
-      <c r="Q18" s="79" t="n"/>
-      <c r="R18" s="79" t="n"/>
-      <c r="S18" s="79" t="n"/>
-      <c r="T18" s="79" t="n"/>
-      <c r="U18" s="150" t="n"/>
-      <c r="V18" s="150">
-        <f>SUM(K18:U18)</f>
-        <v/>
-      </c>
-      <c r="W18" s="150" t="n"/>
-      <c r="X18" s="79" t="n"/>
-      <c r="Y18" s="79" t="n">
-        <v>6430320</v>
-      </c>
-      <c r="Z18" s="150">
-        <f>SUM(W18:Y18)</f>
-        <v/>
-      </c>
-      <c r="AA18" s="151">
-        <f>+V18+Z18</f>
-        <v/>
-      </c>
-      <c r="AB18" s="138" t="inlineStr">
-        <is>
-          <t>4201</t>
-        </is>
-      </c>
-      <c r="AC18" s="71" t="n">
-        <v>156</v>
-      </c>
-      <c r="AD18" s="72" t="n">
-        <v>191</v>
-      </c>
+      <c r="A18" s="60" t="n"/>
+      <c r="B18" s="61" t="n"/>
+      <c r="C18" s="61" t="n"/>
+      <c r="D18" s="61" t="n"/>
+      <c r="E18" s="61" t="n"/>
+      <c r="F18" s="61" t="n"/>
+      <c r="G18" s="61" t="n"/>
+      <c r="H18" s="61" t="n"/>
+      <c r="I18" s="61" t="n"/>
+      <c r="J18" s="61" t="n"/>
+      <c r="K18" s="61" t="n"/>
+      <c r="L18" s="61" t="n"/>
+      <c r="M18" s="61" t="n"/>
+      <c r="N18" s="61" t="n"/>
+      <c r="O18" s="61" t="n"/>
+      <c r="P18" s="61" t="n"/>
+      <c r="Q18" s="61" t="n"/>
+      <c r="R18" s="62" t="n"/>
+      <c r="S18" s="62" t="n"/>
+      <c r="T18" s="62" t="n"/>
+      <c r="U18" s="62" t="n"/>
+      <c r="V18" s="62" t="n"/>
+      <c r="W18" s="62" t="n"/>
+      <c r="X18" s="62" t="n"/>
+      <c r="Y18" s="61" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ 5P VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="Z18" s="63" t="n"/>
+      <c r="AA18" s="63" t="n"/>
+      <c r="AB18" s="63" t="n"/>
+      <c r="AC18" s="55" t="n"/>
+      <c r="AD18" s="55" t="n"/>
+      <c r="AE18" s="50" t="n"/>
+      <c r="AF18" s="50" t="n"/>
+      <c r="AG18" s="50" t="n"/>
+      <c r="AH18" s="50" t="n"/>
+      <c r="AI18" s="50" t="n"/>
+      <c r="AJ18" s="50" t="n"/>
+      <c r="AK18" s="50" t="n"/>
+      <c r="AL18" s="50" t="n"/>
+      <c r="AM18" s="50" t="n"/>
+      <c r="AN18" s="50" t="n"/>
+      <c r="AO18" s="50" t="n"/>
+      <c r="AP18" s="50" t="n"/>
+      <c r="AQ18" s="50" t="n"/>
+      <c r="AR18" s="50" t="n"/>
+      <c r="AS18" s="50" t="n"/>
+      <c r="AT18" s="50" t="n"/>
+      <c r="AU18" s="50" t="n"/>
+      <c r="AV18" s="50" t="n"/>
+      <c r="AW18" s="50" t="n"/>
+      <c r="AX18" s="50" t="n"/>
+      <c r="AY18" s="50" t="n"/>
+      <c r="AZ18" s="50" t="n"/>
+      <c r="BA18" s="50" t="n"/>
+      <c r="BB18" s="50" t="n"/>
+      <c r="BC18" s="50" t="n"/>
+      <c r="BD18" s="50" t="n"/>
+      <c r="BE18" s="50" t="n"/>
+      <c r="BF18" s="50" t="n"/>
+      <c r="BG18" s="50" t="n"/>
+      <c r="BH18" s="50" t="n"/>
+      <c r="BI18" s="50" t="n"/>
+      <c r="BJ18" s="50" t="n"/>
+      <c r="BK18" s="50" t="n"/>
+      <c r="BL18" s="50" t="n"/>
+      <c r="BM18" s="50" t="n"/>
+      <c r="BN18" s="50" t="n"/>
+      <c r="BO18" s="50" t="n"/>
+      <c r="BP18" s="50" t="n"/>
+      <c r="BQ18" s="50" t="n"/>
+      <c r="BR18" s="50" t="n"/>
+      <c r="BS18" s="50" t="n"/>
+      <c r="BT18" s="50" t="n"/>
+      <c r="BU18" s="50" t="n"/>
+      <c r="BV18" s="50" t="n"/>
+      <c r="BW18" s="50" t="n"/>
+      <c r="BX18" s="50" t="n"/>
+      <c r="BY18" s="50" t="n"/>
+      <c r="BZ18" s="50" t="n"/>
+      <c r="CA18" s="50" t="n"/>
+      <c r="CB18" s="50" t="n"/>
+      <c r="CC18" s="50" t="n"/>
+      <c r="CD18" s="50" t="n"/>
+      <c r="CE18" s="50" t="n"/>
+      <c r="CF18" s="50" t="n"/>
+      <c r="CG18" s="50" t="n"/>
+      <c r="CH18" s="50" t="n"/>
+      <c r="CI18" s="50" t="n"/>
+      <c r="CJ18" s="50" t="n"/>
+      <c r="CK18" s="50" t="n"/>
+      <c r="CL18" s="50" t="n"/>
+      <c r="CM18" s="50" t="n"/>
+      <c r="CN18" s="50" t="n"/>
+      <c r="CO18" s="50" t="n"/>
+      <c r="CP18" s="50" t="n"/>
+      <c r="CQ18" s="50" t="n"/>
+      <c r="CR18" s="50" t="n"/>
+      <c r="CS18" s="50" t="n"/>
+      <c r="CT18" s="50" t="n"/>
+      <c r="CU18" s="50" t="n"/>
+      <c r="CV18" s="50" t="n"/>
+      <c r="CW18" s="50" t="n"/>
+      <c r="CX18" s="50" t="n"/>
+      <c r="CY18" s="50" t="n"/>
+      <c r="CZ18" s="50" t="n"/>
+      <c r="DA18" s="50" t="n"/>
+      <c r="DB18" s="50" t="n"/>
+      <c r="DC18" s="50" t="n"/>
+      <c r="DD18" s="50" t="n"/>
+      <c r="DE18" s="50" t="n"/>
+      <c r="DF18" s="50" t="n"/>
+      <c r="DG18" s="50" t="n"/>
+      <c r="DH18" s="50" t="n"/>
+      <c r="DI18" s="50" t="n"/>
+      <c r="DJ18" s="50" t="n"/>
+      <c r="DK18" s="50" t="n"/>
+      <c r="DL18" s="50" t="n"/>
+      <c r="DM18" s="50" t="n"/>
+      <c r="DN18" s="50" t="n"/>
+      <c r="DO18" s="50" t="n"/>
+      <c r="DP18" s="50" t="n"/>
+      <c r="DQ18" s="50" t="n"/>
+      <c r="DR18" s="50" t="n"/>
+      <c r="DS18" s="50" t="n"/>
+      <c r="DT18" s="50" t="n"/>
+      <c r="DU18" s="50" t="n"/>
+      <c r="DV18" s="50" t="n"/>
+      <c r="DW18" s="50" t="n"/>
+      <c r="DX18" s="50" t="n"/>
+      <c r="DY18" s="50" t="n"/>
+      <c r="DZ18" s="50" t="n"/>
+      <c r="EA18" s="50" t="n"/>
+      <c r="EB18" s="50" t="n"/>
+      <c r="EC18" s="50" t="n"/>
+      <c r="ED18" s="50" t="n"/>
+      <c r="EE18" s="50" t="n"/>
+      <c r="EF18" s="50" t="n"/>
+      <c r="EG18" s="50" t="n"/>
+      <c r="EH18" s="50" t="n"/>
+      <c r="EI18" s="50" t="n"/>
+      <c r="EJ18" s="50" t="n"/>
+      <c r="EK18" s="50" t="n"/>
+      <c r="EL18" s="50" t="n"/>
+      <c r="EM18" s="50" t="n"/>
+      <c r="EN18" s="50" t="n"/>
+      <c r="EO18" s="50" t="n"/>
+      <c r="EP18" s="50" t="n"/>
+      <c r="EQ18" s="50" t="n"/>
+      <c r="ER18" s="50" t="n"/>
+      <c r="ES18" s="50" t="n"/>
+      <c r="ET18" s="50" t="n"/>
+      <c r="EU18" s="50" t="n"/>
+      <c r="EV18" s="50" t="n"/>
+      <c r="EW18" s="50" t="n"/>
+      <c r="EX18" s="50" t="n"/>
+      <c r="EY18" s="50" t="n"/>
+      <c r="EZ18" s="50" t="n"/>
+      <c r="FA18" s="50" t="n"/>
+      <c r="FB18" s="50" t="n"/>
+      <c r="FC18" s="50" t="n"/>
+      <c r="FD18" s="50" t="n"/>
+      <c r="FE18" s="50" t="n"/>
+      <c r="FF18" s="50" t="n"/>
+      <c r="FG18" s="50" t="n"/>
+      <c r="FH18" s="50" t="n"/>
+      <c r="FI18" s="50" t="n"/>
+      <c r="FJ18" s="50" t="n"/>
+      <c r="FK18" s="50" t="n"/>
+      <c r="FL18" s="50" t="n"/>
+      <c r="FM18" s="50" t="n"/>
+      <c r="FN18" s="50" t="n"/>
+      <c r="FO18" s="50" t="n"/>
+      <c r="FP18" s="50" t="n"/>
+      <c r="FQ18" s="50" t="n"/>
+      <c r="FR18" s="50" t="n"/>
+      <c r="FS18" s="50" t="n"/>
+      <c r="FT18" s="50" t="n"/>
+      <c r="FU18" s="50" t="n"/>
+      <c r="FV18" s="50" t="n"/>
+      <c r="FW18" s="50" t="n"/>
+      <c r="FX18" s="50" t="n"/>
+      <c r="FY18" s="50" t="n"/>
+      <c r="FZ18" s="50" t="n"/>
+      <c r="GA18" s="50" t="n"/>
+      <c r="GB18" s="50" t="n"/>
+      <c r="GC18" s="50" t="n"/>
+      <c r="GD18" s="50" t="n"/>
+      <c r="GE18" s="50" t="n"/>
+      <c r="GF18" s="50" t="n"/>
+      <c r="GG18" s="50" t="n"/>
+      <c r="GH18" s="50" t="n"/>
+      <c r="GI18" s="50" t="n"/>
+      <c r="GJ18" s="50" t="n"/>
+      <c r="GK18" s="50" t="n"/>
+      <c r="GL18" s="50" t="n"/>
+      <c r="GM18" s="50" t="n"/>
+      <c r="GN18" s="50" t="n"/>
+      <c r="GO18" s="50" t="n"/>
+      <c r="GP18" s="50" t="n"/>
+      <c r="GQ18" s="50" t="n"/>
+      <c r="GR18" s="50" t="n"/>
+      <c r="GS18" s="50" t="n"/>
+      <c r="GT18" s="50" t="n"/>
+      <c r="GU18" s="50" t="n"/>
+      <c r="GV18" s="50" t="n"/>
+      <c r="GW18" s="50" t="n"/>
+      <c r="GX18" s="50" t="n"/>
+      <c r="GY18" s="50" t="n"/>
+      <c r="GZ18" s="50" t="n"/>
+      <c r="HA18" s="50" t="n"/>
+      <c r="HB18" s="50" t="n"/>
+      <c r="HC18" s="50" t="n"/>
+      <c r="HD18" s="50" t="n"/>
+      <c r="HE18" s="50" t="n"/>
+      <c r="HF18" s="50" t="n"/>
+      <c r="HG18" s="50" t="n"/>
+      <c r="HH18" s="50" t="n"/>
+      <c r="HI18" s="50" t="n"/>
+      <c r="HJ18" s="50" t="n"/>
+      <c r="HK18" s="50" t="n"/>
+      <c r="HL18" s="50" t="n"/>
+      <c r="HM18" s="50" t="n"/>
+      <c r="HN18" s="50" t="n"/>
+      <c r="HO18" s="50" t="n"/>
+      <c r="HP18" s="50" t="n"/>
+      <c r="HQ18" s="50" t="n"/>
+      <c r="HR18" s="50" t="n"/>
+      <c r="HS18" s="50" t="n"/>
+      <c r="HT18" s="50" t="n"/>
     </row>
     <row r="19" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A19" s="74" t="n"/>
-      <c r="B19" s="75" t="n"/>
-      <c r="C19" s="75" t="n"/>
-      <c r="D19" s="76" t="n"/>
-      <c r="E19" s="77" t="n"/>
-      <c r="F19" s="76" t="n"/>
-      <c r="G19" s="76" t="n"/>
-      <c r="H19" s="76" t="n"/>
-      <c r="I19" s="76" t="n"/>
-      <c r="J19" s="76" t="n"/>
-      <c r="K19" s="79" t="n"/>
-      <c r="L19" s="150" t="n"/>
-      <c r="M19" s="79" t="n"/>
-      <c r="N19" s="79" t="n"/>
-      <c r="O19" s="79" t="n"/>
-      <c r="P19" s="79" t="n"/>
-      <c r="Q19" s="79" t="n"/>
-      <c r="R19" s="79" t="n"/>
-      <c r="S19" s="79" t="n"/>
-      <c r="T19" s="79" t="n"/>
-      <c r="U19" s="150" t="n"/>
-      <c r="V19" s="150">
-        <f>SUM(K19:U19)</f>
-        <v/>
-      </c>
-      <c r="W19" s="150" t="n"/>
-      <c r="X19" s="79" t="n">
-        <v>60320</v>
-      </c>
-      <c r="Y19" s="79" t="n">
-        <v>6118805</v>
-      </c>
-      <c r="Z19" s="150">
-        <f>SUM(W19:Y19)</f>
-        <v/>
-      </c>
-      <c r="AA19" s="151">
-        <f>+V19+Z19</f>
-        <v/>
-      </c>
-      <c r="AB19" s="138" t="inlineStr">
-        <is>
-          <t>20753, 1237822</t>
-        </is>
-      </c>
-      <c r="AC19" s="71" t="n">
-        <v>164</v>
-      </c>
-      <c r="AD19" s="72" t="n">
-        <v>220</v>
-      </c>
+      <c r="A19" s="29" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="39" t="n"/>
+      <c r="F19" s="33" t="n"/>
+      <c r="G19" s="33" t="n"/>
+      <c r="H19" s="33" t="n"/>
+      <c r="I19" s="33" t="n"/>
+      <c r="J19" s="33" t="n"/>
+      <c r="K19" s="34" t="n"/>
+      <c r="L19" s="45" t="n"/>
+      <c r="M19" s="34" t="n"/>
+      <c r="N19" s="31" t="n"/>
+      <c r="O19" s="31" t="n"/>
+      <c r="P19" s="31" t="n"/>
+      <c r="Q19" s="31" t="n"/>
+      <c r="R19" s="31" t="n"/>
+      <c r="S19" s="31" t="n"/>
+      <c r="T19" s="35" t="n"/>
+      <c r="U19" s="31" t="n"/>
+      <c r="V19" s="31" t="n"/>
+      <c r="W19" s="31" t="n"/>
+      <c r="X19" s="31" t="n"/>
+      <c r="Y19" s="31" t="n"/>
+      <c r="Z19" s="31" t="n"/>
+      <c r="AA19" s="31" t="n"/>
+      <c r="AB19" s="31" t="n"/>
+      <c r="AC19" s="31" t="n"/>
+      <c r="AD19" s="36" t="n"/>
     </row>
     <row r="20" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A20" s="74" t="n"/>
-      <c r="B20" s="75" t="n"/>
-      <c r="C20" s="75" t="n"/>
-      <c r="D20" s="76" t="n"/>
-      <c r="E20" s="77" t="n"/>
-      <c r="F20" s="76" t="n"/>
-      <c r="G20" s="76" t="n"/>
-      <c r="H20" s="76" t="n"/>
-      <c r="I20" s="76" t="n"/>
-      <c r="J20" s="76" t="n"/>
-      <c r="K20" s="79" t="n"/>
-      <c r="L20" s="150" t="n"/>
-      <c r="M20" s="79" t="n"/>
-      <c r="N20" s="79" t="n"/>
-      <c r="O20" s="79" t="n"/>
-      <c r="P20" s="79" t="n"/>
-      <c r="Q20" s="79" t="n"/>
-      <c r="R20" s="79" t="n"/>
-      <c r="S20" s="79" t="n"/>
-      <c r="T20" s="79" t="n"/>
-      <c r="U20" s="150" t="n"/>
-      <c r="V20" s="150">
-        <f>SUM(K20:U20)</f>
-        <v/>
-      </c>
-      <c r="W20" s="150" t="n"/>
-      <c r="X20" s="79" t="n"/>
-      <c r="Y20" s="79" t="n">
-        <v>813240</v>
-      </c>
-      <c r="Z20" s="150">
-        <f>SUM(W20:Y20)</f>
-        <v/>
-      </c>
-      <c r="AA20" s="151">
-        <f>+V20+Z20</f>
-        <v/>
-      </c>
-      <c r="AB20" s="138" t="inlineStr">
-        <is>
-          <t>21031</t>
-        </is>
-      </c>
-      <c r="AC20" s="71" t="n">
-        <v>166</v>
-      </c>
-      <c r="AD20" s="72" t="n">
-        <v>221</v>
-      </c>
+      <c r="A20" s="29" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="30" t="n"/>
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="33" t="n"/>
+      <c r="J20" s="33" t="n"/>
+      <c r="K20" s="38" t="n"/>
+      <c r="L20" s="38" t="n"/>
+      <c r="M20" s="44" t="n"/>
+      <c r="N20" s="33" t="n"/>
+      <c r="O20" s="33" t="n"/>
+      <c r="P20" s="33" t="n"/>
+      <c r="Q20" s="33" t="n"/>
+      <c r="R20" s="33" t="n"/>
+      <c r="S20" s="33" t="n"/>
+      <c r="T20" s="158" t="n"/>
+      <c r="U20" s="33" t="n"/>
+      <c r="AA20" s="35" t="n"/>
+      <c r="AB20" s="35" t="n"/>
+      <c r="AD20" s="36" t="n"/>
+      <c r="AE20" s="55" t="n"/>
     </row>
     <row r="21" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A21" s="74" t="n"/>
-      <c r="B21" s="75" t="n"/>
-      <c r="C21" s="75" t="n"/>
-      <c r="D21" s="76" t="n"/>
-      <c r="E21" s="77" t="n"/>
-      <c r="F21" s="76" t="n"/>
-      <c r="G21" s="76" t="n"/>
-      <c r="H21" s="76" t="n"/>
-      <c r="I21" s="76" t="n"/>
-      <c r="J21" s="76" t="n"/>
-      <c r="K21" s="79" t="n"/>
-      <c r="L21" s="150" t="n"/>
-      <c r="M21" s="79" t="n"/>
-      <c r="N21" s="79" t="n"/>
-      <c r="O21" s="79" t="n"/>
-      <c r="P21" s="79" t="n"/>
-      <c r="Q21" s="79" t="n"/>
-      <c r="R21" s="79" t="n"/>
-      <c r="S21" s="79" t="n"/>
-      <c r="T21" s="79" t="n"/>
-      <c r="U21" s="150" t="n"/>
-      <c r="V21" s="150">
-        <f>SUM(K21:U21)</f>
-        <v/>
-      </c>
-      <c r="W21" s="150" t="n">
-        <v>3150575</v>
-      </c>
-      <c r="X21" s="79" t="n"/>
-      <c r="Y21" s="79" t="n">
-        <v>1018440</v>
-      </c>
-      <c r="Z21" s="150">
-        <f>SUM(W21:Y21)</f>
-        <v/>
-      </c>
-      <c r="AA21" s="151">
-        <f>+V21+Z21</f>
-        <v/>
-      </c>
-      <c r="AB21" s="138" t="inlineStr">
-        <is>
-          <t>4705</t>
-        </is>
-      </c>
-      <c r="AC21" s="71" t="n">
-        <v>167</v>
-      </c>
-      <c r="AD21" s="72" t="n">
-        <v>222</v>
-      </c>
+      <c r="C21" s="37" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="30" t="n"/>
+      <c r="K21" s="38" t="n"/>
+      <c r="L21" s="38" t="n"/>
+      <c r="M21" s="38" t="n"/>
+      <c r="N21" s="33" t="n"/>
+      <c r="O21" s="33" t="n"/>
+      <c r="P21" s="33" t="n"/>
+      <c r="Q21" s="33" t="n"/>
+      <c r="R21" s="33" t="n"/>
+      <c r="S21" s="33" t="n"/>
+      <c r="T21" s="33" t="n"/>
+      <c r="U21" s="33" t="n"/>
+      <c r="AA21" s="35" t="n"/>
+      <c r="AD21" s="36" t="n"/>
+      <c r="AE21" s="36" t="n"/>
     </row>
     <row r="22" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A22" s="74" t="n"/>
-      <c r="B22" s="75" t="n"/>
-      <c r="C22" s="75" t="n"/>
-      <c r="D22" s="76" t="n"/>
-      <c r="E22" s="77" t="n"/>
-      <c r="F22" s="76" t="n"/>
-      <c r="G22" s="76" t="n"/>
-      <c r="H22" s="76" t="n"/>
-      <c r="I22" s="76" t="n"/>
-      <c r="J22" s="76" t="n"/>
-      <c r="K22" s="79" t="n"/>
-      <c r="L22" s="150" t="n"/>
-      <c r="M22" s="79" t="n"/>
-      <c r="N22" s="79" t="n"/>
-      <c r="O22" s="79" t="n"/>
-      <c r="P22" s="79" t="n"/>
-      <c r="Q22" s="79" t="n"/>
-      <c r="R22" s="79" t="n"/>
-      <c r="S22" s="79" t="n"/>
-      <c r="T22" s="79" t="n"/>
-      <c r="U22" s="150" t="n"/>
-      <c r="V22" s="150">
-        <f>SUM(K22:U22)</f>
-        <v/>
-      </c>
-      <c r="W22" s="150" t="n">
-        <v>8315789</v>
-      </c>
-      <c r="X22" s="79" t="n"/>
-      <c r="Y22" s="79" t="n">
-        <v>923400</v>
-      </c>
-      <c r="Z22" s="150">
-        <f>SUM(W22:Y22)</f>
-        <v/>
-      </c>
-      <c r="AA22" s="151">
-        <f>+V22+Z22</f>
-        <v/>
-      </c>
-      <c r="AB22" s="138" t="inlineStr">
-        <is>
-          <t>3549</t>
-        </is>
-      </c>
-      <c r="AC22" s="71" t="n">
-        <v>170</v>
-      </c>
-      <c r="AD22" s="72" t="n">
-        <v>223</v>
-      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="32" t="n"/>
+      <c r="E22" s="39" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="39" t="n"/>
+      <c r="K22" s="38" t="n"/>
+      <c r="L22" s="38" t="n"/>
+      <c r="M22" s="38" t="n"/>
+      <c r="N22" s="33" t="n"/>
+      <c r="O22" s="33" t="n"/>
+      <c r="P22" s="33" t="n"/>
+      <c r="Q22" s="33" t="n"/>
+      <c r="R22" s="33" t="n"/>
+      <c r="S22" s="33" t="n"/>
+      <c r="T22" s="33" t="n"/>
+      <c r="U22" s="33" t="n"/>
+      <c r="AD22" s="36" t="n"/>
+      <c r="AE22" s="36" t="n"/>
     </row>
     <row r="23" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A23" s="74" t="n"/>
-      <c r="B23" s="75" t="n"/>
-      <c r="C23" s="75" t="n"/>
-      <c r="D23" s="76" t="n"/>
-      <c r="E23" s="77" t="n"/>
-      <c r="F23" s="76" t="n"/>
-      <c r="G23" s="76" t="n"/>
-      <c r="H23" s="76" t="n"/>
-      <c r="I23" s="76" t="n"/>
-      <c r="J23" s="76" t="n"/>
-      <c r="K23" s="79" t="n"/>
-      <c r="L23" s="150" t="n"/>
-      <c r="M23" s="79" t="n"/>
-      <c r="N23" s="79" t="n"/>
-      <c r="O23" s="79" t="n"/>
-      <c r="P23" s="79" t="n"/>
-      <c r="Q23" s="79" t="n"/>
-      <c r="R23" s="79" t="n"/>
-      <c r="S23" s="79" t="n"/>
-      <c r="T23" s="79" t="n"/>
-      <c r="U23" s="150" t="n"/>
-      <c r="V23" s="150">
-        <f>SUM(K23:U23)</f>
-        <v/>
-      </c>
-      <c r="W23" s="150" t="n">
-        <v>8315789</v>
-      </c>
-      <c r="X23" s="79" t="n">
-        <v>250000</v>
-      </c>
-      <c r="Y23" s="79">
-        <f>1188000+1620000</f>
-        <v/>
-      </c>
-      <c r="Z23" s="150">
-        <f>SUM(W23:Y23)</f>
-        <v/>
-      </c>
-      <c r="AA23" s="151">
-        <f>+V23+Z23</f>
-        <v/>
-      </c>
-      <c r="AB23" s="138" t="inlineStr">
-        <is>
-          <t>52914, 82584, 1246237</t>
-        </is>
-      </c>
-      <c r="AC23" s="71" t="n">
-        <v>175</v>
-      </c>
-      <c r="AD23" s="72" t="n">
-        <v>224</v>
-      </c>
+      <c r="B23" s="33" t="n"/>
+      <c r="C23" s="33" t="n"/>
+      <c r="D23" s="33" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="33" t="n"/>
+      <c r="G23" s="33" t="n"/>
+      <c r="H23" s="33" t="n"/>
+      <c r="I23" s="33" t="n"/>
+      <c r="J23" s="33" t="n"/>
+      <c r="K23" s="33" t="n"/>
+      <c r="L23" s="33" t="n"/>
+      <c r="M23" s="33" t="n"/>
+      <c r="N23" s="33" t="n"/>
+      <c r="O23" s="33" t="n"/>
+      <c r="P23" s="33" t="n"/>
+      <c r="Q23" s="33" t="n"/>
+      <c r="T23" s="40" t="n"/>
+      <c r="W23" s="30" t="n"/>
+      <c r="X23" s="33" t="n"/>
+      <c r="Y23" s="33" t="n"/>
+      <c r="Z23" s="33" t="n"/>
+      <c r="AD23" s="36" t="n"/>
+      <c r="AE23" s="36" t="n"/>
     </row>
     <row r="24" ht="49.5" customFormat="1" customHeight="1" s="59">
-      <c r="A24" s="74" t="n"/>
-      <c r="B24" s="82" t="n"/>
-      <c r="C24" s="82" t="n"/>
-      <c r="D24" s="82" t="n"/>
-      <c r="E24" s="83" t="n"/>
-      <c r="F24" s="76" t="n"/>
-      <c r="G24" s="76" t="n"/>
-      <c r="H24" s="82" t="n"/>
-      <c r="I24" s="84" t="n"/>
-      <c r="J24" s="71" t="n"/>
-      <c r="K24" s="85" t="n"/>
-      <c r="L24" s="150" t="n"/>
-      <c r="M24" s="85" t="n"/>
-      <c r="N24" s="150" t="n"/>
-      <c r="O24" s="150" t="n"/>
-      <c r="P24" s="85" t="n"/>
-      <c r="Q24" s="85" t="n"/>
-      <c r="R24" s="86" t="n"/>
-      <c r="S24" s="150" t="n"/>
-      <c r="T24" s="85" t="n"/>
-      <c r="U24" s="150" t="n"/>
-      <c r="V24" s="150">
-        <f>SUM(K24:U24)</f>
-        <v/>
-      </c>
-      <c r="W24" s="150" t="n"/>
-      <c r="X24" s="150" t="n"/>
-      <c r="Y24" s="85" t="n">
-        <v>390053</v>
-      </c>
-      <c r="Z24" s="150">
-        <f>SUM(W24:Y24)</f>
-        <v/>
-      </c>
-      <c r="AA24" s="151">
-        <f>+V24+Z24</f>
-        <v/>
-      </c>
-      <c r="AB24" s="139" t="inlineStr">
-        <is>
-          <t>00021776</t>
-        </is>
-      </c>
-      <c r="AC24" s="71" t="n">
-        <v>155</v>
-      </c>
-      <c r="AD24" s="72" t="n">
-        <v>178</v>
-      </c>
+      <c r="A24" s="19" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="42" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
+      <c r="I24" s="16" t="n"/>
+      <c r="J24" s="16" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="16" t="n"/>
+      <c r="O24" s="16" t="n"/>
+      <c r="P24" s="16" t="n"/>
+      <c r="Q24" s="16" t="n"/>
+      <c r="R24" s="16" t="n"/>
+      <c r="S24" s="16" t="n"/>
+      <c r="T24" s="16" t="n"/>
+      <c r="U24" s="16" t="n"/>
+      <c r="V24" s="16" t="n"/>
+      <c r="W24" s="16" t="n"/>
+      <c r="X24" s="16" t="n"/>
+      <c r="Y24" s="16" t="n"/>
+      <c r="Z24" s="16" t="n"/>
+      <c r="AA24" s="16" t="n"/>
+      <c r="AB24" s="16" t="n"/>
+      <c r="AC24" s="16" t="n"/>
+      <c r="AD24" s="20" t="n"/>
+      <c r="AE24" s="36" t="n"/>
     </row>
     <row r="25" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A25" s="74" t="n"/>
-      <c r="B25" s="82" t="n"/>
-      <c r="C25" s="82" t="n"/>
-      <c r="D25" s="82" t="n"/>
-      <c r="E25" s="83" t="n"/>
-      <c r="F25" s="76" t="n"/>
-      <c r="G25" s="76" t="n"/>
-      <c r="H25" s="82" t="n"/>
-      <c r="I25" s="84" t="n"/>
-      <c r="J25" s="71" t="n"/>
-      <c r="K25" s="85" t="n"/>
-      <c r="L25" s="150" t="n"/>
-      <c r="M25" s="85" t="n"/>
-      <c r="N25" s="150" t="n"/>
-      <c r="O25" s="150" t="n"/>
-      <c r="P25" s="85" t="n"/>
-      <c r="Q25" s="85" t="n"/>
-      <c r="R25" s="86" t="n"/>
-      <c r="S25" s="150" t="n"/>
-      <c r="T25" s="85" t="n"/>
-      <c r="U25" s="150" t="n"/>
-      <c r="V25" s="150">
-        <f>SUM(K25:U25)</f>
-        <v/>
-      </c>
-      <c r="W25" s="150" t="n"/>
-      <c r="X25" s="150" t="n"/>
-      <c r="Y25" s="85" t="n">
-        <v>641952</v>
-      </c>
-      <c r="Z25" s="150">
-        <f>SUM(W25:Y25)</f>
-        <v/>
-      </c>
-      <c r="AA25" s="151">
-        <f>+V25+Z25</f>
-        <v/>
-      </c>
-      <c r="AB25" s="139" t="inlineStr">
-        <is>
-          <t>00026617</t>
-        </is>
-      </c>
-      <c r="AC25" s="71" t="n">
-        <v>163</v>
-      </c>
-      <c r="AD25" s="72" t="n">
-        <v>179</v>
-      </c>
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="42" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="16" t="n"/>
+      <c r="J25" s="16" t="n"/>
+      <c r="K25" s="16" t="n"/>
+      <c r="L25" s="16" t="n"/>
+      <c r="M25" s="16" t="n"/>
+      <c r="N25" s="16" t="n"/>
+      <c r="O25" s="16" t="n"/>
+      <c r="P25" s="16" t="n"/>
+      <c r="Q25" s="16" t="n"/>
+      <c r="R25" s="16" t="n"/>
+      <c r="S25" s="16" t="n"/>
+      <c r="T25" s="16" t="n"/>
+      <c r="U25" s="16" t="n"/>
+      <c r="V25" s="16" t="n"/>
+      <c r="W25" s="16" t="n"/>
+      <c r="X25" s="16" t="n"/>
+      <c r="Y25" s="16" t="n"/>
+      <c r="Z25" s="16" t="n"/>
+      <c r="AA25" s="16" t="n"/>
+      <c r="AB25" s="16" t="n"/>
+      <c r="AC25" s="16" t="n"/>
+      <c r="AD25" s="16" t="n"/>
+      <c r="AE25" s="41" t="n"/>
     </row>
     <row r="26" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A26" s="74" t="n"/>
-      <c r="B26" s="82" t="n"/>
-      <c r="C26" s="82" t="n"/>
-      <c r="D26" s="82" t="n"/>
-      <c r="E26" s="83" t="n"/>
-      <c r="F26" s="87" t="n"/>
-      <c r="G26" s="76" t="n"/>
-      <c r="H26" s="82" t="n"/>
-      <c r="I26" s="84" t="n"/>
-      <c r="J26" s="71" t="n"/>
-      <c r="K26" s="85" t="n"/>
-      <c r="L26" s="150" t="n"/>
-      <c r="M26" s="85" t="n"/>
-      <c r="N26" s="150" t="n"/>
-      <c r="O26" s="150" t="n"/>
-      <c r="P26" s="85" t="n"/>
-      <c r="Q26" s="85" t="n"/>
-      <c r="R26" s="86" t="n"/>
-      <c r="S26" s="150" t="n"/>
-      <c r="T26" s="85" t="n"/>
-      <c r="U26" s="150" t="n"/>
-      <c r="V26" s="150">
-        <f>SUM(K26:U26)</f>
-        <v/>
-      </c>
-      <c r="W26" s="150" t="n"/>
-      <c r="X26" s="150" t="n"/>
-      <c r="Y26" s="85" t="n">
-        <v>973166</v>
-      </c>
-      <c r="Z26" s="150">
-        <f>SUM(W26:Y26)</f>
-        <v/>
-      </c>
-      <c r="AA26" s="151">
-        <f>+V26+Z26</f>
-        <v/>
-      </c>
-      <c r="AB26" s="139" t="inlineStr">
-        <is>
-          <t>00026618</t>
-        </is>
-      </c>
-      <c r="AC26" s="71" t="n">
-        <v>162</v>
-      </c>
-      <c r="AD26" s="72" t="n">
-        <v>180</v>
-      </c>
+      <c r="A26" s="19" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="42" t="n"/>
+      <c r="K26" s="16" t="n"/>
+      <c r="L26" s="16" t="n"/>
+      <c r="M26" s="16" t="n"/>
+      <c r="AB26" s="16" t="n"/>
+      <c r="AE26" s="20" t="n"/>
     </row>
     <row r="27" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A27" s="74" t="n"/>
-      <c r="B27" s="82" t="n"/>
-      <c r="C27" s="82" t="n"/>
-      <c r="D27" s="82" t="n"/>
-      <c r="E27" s="83" t="n"/>
-      <c r="F27" s="87" t="n"/>
-      <c r="G27" s="76" t="n"/>
-      <c r="H27" s="82" t="n"/>
-      <c r="I27" s="84" t="n"/>
-      <c r="J27" s="71" t="n"/>
-      <c r="K27" s="85" t="n"/>
-      <c r="L27" s="150" t="n"/>
-      <c r="M27" s="85" t="n"/>
-      <c r="N27" s="150" t="n"/>
-      <c r="O27" s="150" t="n"/>
-      <c r="P27" s="85" t="n"/>
-      <c r="Q27" s="85" t="n"/>
-      <c r="R27" s="85" t="n"/>
-      <c r="S27" s="150" t="n"/>
-      <c r="T27" s="85" t="n"/>
-      <c r="U27" s="150" t="n"/>
-      <c r="V27" s="150">
-        <f>SUM(K27:U27)</f>
-        <v/>
-      </c>
-      <c r="W27" s="150" t="n"/>
-      <c r="X27" s="150" t="n"/>
-      <c r="Y27" s="85" t="n"/>
-      <c r="Z27" s="150">
-        <f>SUM(W27:Y27)</f>
-        <v/>
-      </c>
-      <c r="AA27" s="151">
-        <f>+V27+Z27</f>
-        <v/>
-      </c>
-      <c r="AB27" s="139" t="n"/>
-      <c r="AC27" s="71" t="n">
-        <v>176</v>
-      </c>
-      <c r="AD27" s="72" t="n">
-        <v>181</v>
-      </c>
+      <c r="A27" s="19" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="42" t="n"/>
+      <c r="K27" s="16" t="n"/>
+      <c r="L27" s="16" t="n"/>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="18" t="n"/>
+      <c r="P27" s="18" t="n"/>
+      <c r="Q27" s="18" t="n"/>
+      <c r="R27" s="18" t="n"/>
+      <c r="S27" s="18" t="n"/>
+      <c r="T27" s="18" t="n"/>
+      <c r="U27" s="18" t="n"/>
+      <c r="V27" s="18" t="n"/>
+      <c r="W27" s="18" t="n"/>
+      <c r="X27" s="18" t="n"/>
+      <c r="Y27" s="18" t="n"/>
+      <c r="Z27" s="18" t="n"/>
+      <c r="AA27" s="18" t="n"/>
+      <c r="AB27" s="18" t="n"/>
+      <c r="AC27" s="18" t="n"/>
+      <c r="AD27" s="18" t="n"/>
     </row>
     <row r="28" ht="37" customFormat="1" customHeight="1" s="59" thickBot="1">
-      <c r="A28" s="121" t="n"/>
-      <c r="B28" s="122" t="n"/>
-      <c r="C28" s="122" t="n"/>
-      <c r="D28" s="122" t="n"/>
-      <c r="E28" s="123" t="n"/>
-      <c r="F28" s="124" t="n"/>
-      <c r="G28" s="124" t="n"/>
-      <c r="H28" s="122" t="n"/>
-      <c r="I28" s="125" t="n"/>
-      <c r="J28" s="126" t="n"/>
-      <c r="K28" s="127" t="n"/>
-      <c r="L28" s="152" t="n"/>
-      <c r="M28" s="127" t="n"/>
-      <c r="N28" s="152" t="n"/>
-      <c r="O28" s="152" t="n"/>
-      <c r="P28" s="127" t="n"/>
-      <c r="Q28" s="127" t="n"/>
-      <c r="R28" s="129" t="n"/>
-      <c r="S28" s="152" t="n"/>
-      <c r="T28" s="127" t="n"/>
-      <c r="U28" s="152" t="n"/>
-      <c r="V28" s="152">
-        <f>SUM(K28:U28)</f>
-        <v/>
-      </c>
-      <c r="W28" s="152" t="n"/>
-      <c r="X28" s="152" t="n"/>
-      <c r="Y28" s="127" t="n">
-        <v>675367</v>
-      </c>
-      <c r="Z28" s="152">
-        <f>SUM(W28:Y28)</f>
-        <v/>
-      </c>
-      <c r="AA28" s="153">
-        <f>+V28+Z28</f>
-        <v/>
-      </c>
-      <c r="AB28" s="140" t="inlineStr">
-        <is>
-          <t>00031718</t>
-        </is>
-      </c>
-      <c r="AC28" s="116" t="n">
-        <v>177</v>
-      </c>
-      <c r="AD28" s="117" t="n">
-        <v>182</v>
-      </c>
+      <c r="A28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="K28" s="16" t="n"/>
+      <c r="L28" s="16" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="18" t="n"/>
+      <c r="P28" s="18" t="n"/>
+      <c r="Q28" s="18" t="n"/>
+      <c r="R28" s="18" t="n"/>
+      <c r="S28" s="18" t="n"/>
+      <c r="T28" s="18" t="n"/>
+      <c r="U28" s="18" t="n"/>
+      <c r="V28" s="18" t="n"/>
+      <c r="W28" s="18" t="n"/>
+      <c r="X28" s="18" t="n"/>
+      <c r="Y28" s="18" t="n"/>
+      <c r="Z28" s="18" t="n"/>
+      <c r="AA28" s="18" t="n"/>
+      <c r="AB28" s="18" t="n"/>
+      <c r="AC28" s="18" t="n"/>
+      <c r="AD28" s="18" t="n"/>
     </row>
     <row r="29" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A29" s="98" t="n"/>
-      <c r="B29" s="141" t="n"/>
-      <c r="C29" s="141" t="n"/>
-      <c r="D29" s="141" t="n"/>
-      <c r="E29" s="141" t="n"/>
-      <c r="F29" s="141" t="n"/>
-      <c r="G29" s="141" t="n"/>
-      <c r="H29" s="141" t="n"/>
-      <c r="I29" s="141" t="n"/>
-      <c r="J29" s="142" t="n"/>
-      <c r="K29" s="64" t="n"/>
-      <c r="L29" s="64" t="n"/>
-      <c r="M29" s="64" t="n"/>
-      <c r="N29" s="64" t="n"/>
-      <c r="O29" s="64" t="n"/>
-      <c r="P29" s="64" t="n"/>
-      <c r="Q29" s="64" t="n"/>
-      <c r="R29" s="64" t="n"/>
-      <c r="S29" s="64" t="n"/>
-      <c r="T29" s="64" t="n"/>
-      <c r="U29" s="64">
-        <f>SUM(U13:U28)</f>
-        <v/>
-      </c>
-      <c r="V29" s="64">
-        <f>SUM(V13:V28)</f>
-        <v/>
-      </c>
-      <c r="W29" s="64">
-        <f>SUM(W13:W28)</f>
-        <v/>
-      </c>
-      <c r="X29" s="64">
-        <f>SUM(X13:X28)</f>
-        <v/>
-      </c>
-      <c r="Y29" s="64">
-        <f>SUM(Y13:Y28)</f>
-        <v/>
-      </c>
-      <c r="Z29" s="64">
-        <f>SUM(Z13:Z28)</f>
-        <v/>
-      </c>
-      <c r="AA29" s="65">
-        <f>SUM(AA13:AA28)</f>
-        <v/>
-      </c>
-      <c r="AB29" s="56" t="n"/>
-      <c r="AC29" s="50" t="n"/>
-      <c r="AD29" s="50" t="n"/>
+      <c r="A29" s="88" t="n"/>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="16" t="n"/>
+      <c r="I29" s="16" t="n"/>
+      <c r="J29" s="16" t="n"/>
+      <c r="K29" s="16" t="n"/>
+      <c r="L29" s="16" t="n"/>
+      <c r="M29" s="16" t="n"/>
+      <c r="N29" s="16" t="n"/>
+      <c r="O29" s="16" t="n"/>
+      <c r="P29" s="16" t="n"/>
+      <c r="Q29" s="16" t="n"/>
+      <c r="R29" s="16" t="n"/>
+      <c r="S29" s="16" t="n"/>
+      <c r="T29" s="16" t="n"/>
+      <c r="U29" s="16" t="n"/>
+      <c r="V29" s="16" t="n"/>
+      <c r="W29" s="16" t="n"/>
+      <c r="X29" s="16" t="n"/>
+      <c r="Y29" s="16" t="n"/>
+      <c r="Z29" s="16" t="n"/>
+      <c r="AA29" s="16" t="n"/>
+      <c r="AB29" s="16" t="n"/>
+      <c r="AC29" s="16" t="n"/>
+      <c r="AD29" s="16" t="n"/>
     </row>
     <row r="30" ht="37" customFormat="1" customHeight="1" s="59">
-      <c r="A30" s="100" t="n"/>
-      <c r="B30" s="154" t="n"/>
-      <c r="C30" s="154" t="n"/>
-      <c r="D30" s="154" t="n"/>
-      <c r="E30" s="154" t="n"/>
-      <c r="F30" s="154" t="n"/>
-      <c r="G30" s="154" t="n"/>
-      <c r="H30" s="154" t="n"/>
-      <c r="I30" s="154" t="n"/>
-      <c r="J30" s="155" t="n"/>
-      <c r="K30" s="27" t="n"/>
-      <c r="L30" s="27" t="n"/>
-      <c r="M30" s="27" t="n"/>
-      <c r="N30" s="27" t="n"/>
-      <c r="O30" s="27" t="n"/>
-      <c r="P30" s="27" t="n"/>
-      <c r="Q30" s="27" t="n"/>
-      <c r="R30" s="27" t="n"/>
-      <c r="S30" s="27" t="n"/>
-      <c r="T30" s="27" t="n"/>
-      <c r="U30" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="52" t="n"/>
-      <c r="AC30" s="23" t="n"/>
-      <c r="AD30" s="23" t="n"/>
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="42" t="n"/>
+      <c r="E30" s="88" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="16" t="n"/>
+      <c r="I30" s="16" t="n"/>
+      <c r="J30" s="16" t="n"/>
+      <c r="K30" s="16" t="n"/>
+      <c r="L30" s="16" t="n"/>
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="16" t="n"/>
+      <c r="O30" s="16" t="n"/>
+      <c r="P30" s="16" t="n"/>
+      <c r="Q30" s="16" t="n"/>
+      <c r="R30" s="16" t="n"/>
+      <c r="S30" s="16" t="n"/>
+      <c r="T30" s="16" t="n"/>
+      <c r="U30" s="16" t="n"/>
+      <c r="V30" s="16" t="n"/>
+      <c r="W30" s="16" t="n"/>
+      <c r="X30" s="16" t="n"/>
+      <c r="Y30" s="16" t="n"/>
+      <c r="Z30" s="16" t="n"/>
+      <c r="AA30" s="16" t="n"/>
+      <c r="AB30" s="16" t="n"/>
+      <c r="AC30" s="16" t="n"/>
+      <c r="AD30" s="16" t="n"/>
     </row>
     <row r="31" ht="32" customFormat="1" customHeight="1" s="51" thickBot="1">
-      <c r="A31" s="102" t="n"/>
-      <c r="B31" s="156" t="n"/>
-      <c r="C31" s="156" t="n"/>
-      <c r="D31" s="156" t="n"/>
-      <c r="E31" s="156" t="n"/>
-      <c r="F31" s="156" t="n"/>
-      <c r="G31" s="156" t="n"/>
-      <c r="H31" s="156" t="n"/>
-      <c r="I31" s="156" t="n"/>
-      <c r="J31" s="157" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="13" t="n"/>
-      <c r="M31" s="13" t="n"/>
-      <c r="N31" s="13" t="n"/>
-      <c r="O31" s="13" t="n"/>
-      <c r="P31" s="13" t="n"/>
-      <c r="Q31" s="13" t="n"/>
-      <c r="R31" s="13" t="n"/>
-      <c r="S31" s="13" t="n"/>
-      <c r="T31" s="13" t="n"/>
-      <c r="U31" s="13">
-        <f>SUM(U29:U30)</f>
-        <v/>
-      </c>
-      <c r="V31" s="13">
-        <f>SUM(V29:V30)</f>
-        <v/>
-      </c>
-      <c r="W31" s="13">
-        <f>SUM(W29:W30)</f>
-        <v/>
-      </c>
-      <c r="X31" s="13">
-        <f>SUM(X29:X30)</f>
-        <v/>
-      </c>
-      <c r="Y31" s="13">
-        <f>SUM(Y29:Y30)</f>
-        <v/>
-      </c>
-      <c r="Z31" s="13">
-        <f>SUM(Z29:Z30)</f>
-        <v/>
-      </c>
-      <c r="AA31" s="47">
-        <f>SUM(AA29:AA30)</f>
-        <v/>
-      </c>
-      <c r="AB31" s="49" t="n"/>
-      <c r="AC31" s="50" t="n"/>
-      <c r="AD31" s="50" t="n"/>
-      <c r="AE31" s="50" t="n"/>
-      <c r="AF31" s="50" t="n"/>
-      <c r="AG31" s="50" t="n"/>
-      <c r="AH31" s="50" t="n"/>
-      <c r="AI31" s="50" t="n"/>
-      <c r="AJ31" s="50" t="n"/>
-      <c r="AK31" s="50" t="n"/>
-      <c r="AL31" s="50" t="n"/>
-      <c r="AM31" s="50" t="n"/>
-      <c r="AN31" s="50" t="n"/>
-      <c r="AO31" s="50" t="n"/>
-      <c r="AP31" s="50" t="n"/>
-      <c r="AQ31" s="50" t="n"/>
-      <c r="AR31" s="50" t="n"/>
-      <c r="AS31" s="50" t="n"/>
-      <c r="AT31" s="50" t="n"/>
-      <c r="AU31" s="50" t="n"/>
-      <c r="AV31" s="50" t="n"/>
-      <c r="AW31" s="50" t="n"/>
-      <c r="AX31" s="50" t="n"/>
-      <c r="AY31" s="50" t="n"/>
-      <c r="AZ31" s="50" t="n"/>
-      <c r="BA31" s="50" t="n"/>
-      <c r="BB31" s="50" t="n"/>
-      <c r="BC31" s="50" t="n"/>
-      <c r="BD31" s="50" t="n"/>
-      <c r="BE31" s="50" t="n"/>
-      <c r="BF31" s="50" t="n"/>
-      <c r="BG31" s="50" t="n"/>
-      <c r="BH31" s="50" t="n"/>
-      <c r="BI31" s="50" t="n"/>
-      <c r="BJ31" s="50" t="n"/>
-      <c r="BK31" s="50" t="n"/>
-      <c r="BL31" s="50" t="n"/>
-      <c r="BM31" s="50" t="n"/>
-      <c r="BN31" s="50" t="n"/>
-      <c r="BO31" s="50" t="n"/>
-      <c r="BP31" s="50" t="n"/>
-      <c r="BQ31" s="50" t="n"/>
-      <c r="BR31" s="50" t="n"/>
-      <c r="BS31" s="50" t="n"/>
-      <c r="BT31" s="50" t="n"/>
-      <c r="BU31" s="50" t="n"/>
-      <c r="BV31" s="50" t="n"/>
-      <c r="BW31" s="50" t="n"/>
-      <c r="BX31" s="50" t="n"/>
-      <c r="BY31" s="50" t="n"/>
-      <c r="BZ31" s="50" t="n"/>
-      <c r="CA31" s="50" t="n"/>
-      <c r="CB31" s="50" t="n"/>
-      <c r="CC31" s="50" t="n"/>
-      <c r="CD31" s="50" t="n"/>
-      <c r="CE31" s="50" t="n"/>
-      <c r="CF31" s="50" t="n"/>
-      <c r="CG31" s="50" t="n"/>
-      <c r="CH31" s="50" t="n"/>
-      <c r="CI31" s="50" t="n"/>
-      <c r="CJ31" s="50" t="n"/>
-      <c r="CK31" s="50" t="n"/>
-      <c r="CL31" s="50" t="n"/>
-      <c r="CM31" s="50" t="n"/>
-      <c r="CN31" s="50" t="n"/>
-      <c r="CO31" s="50" t="n"/>
-      <c r="CP31" s="50" t="n"/>
-      <c r="CQ31" s="50" t="n"/>
-      <c r="CR31" s="50" t="n"/>
-      <c r="CS31" s="50" t="n"/>
-      <c r="CT31" s="50" t="n"/>
-      <c r="CU31" s="50" t="n"/>
-      <c r="CV31" s="50" t="n"/>
-      <c r="CW31" s="50" t="n"/>
-      <c r="CX31" s="50" t="n"/>
-      <c r="CY31" s="50" t="n"/>
-      <c r="CZ31" s="50" t="n"/>
-      <c r="DA31" s="50" t="n"/>
-      <c r="DB31" s="50" t="n"/>
-      <c r="DC31" s="50" t="n"/>
-      <c r="DD31" s="50" t="n"/>
-      <c r="DE31" s="50" t="n"/>
-      <c r="DF31" s="50" t="n"/>
-      <c r="DG31" s="50" t="n"/>
-      <c r="DH31" s="50" t="n"/>
-      <c r="DI31" s="50" t="n"/>
-      <c r="DJ31" s="50" t="n"/>
-      <c r="DK31" s="50" t="n"/>
-      <c r="DL31" s="50" t="n"/>
-      <c r="DM31" s="50" t="n"/>
-      <c r="DN31" s="50" t="n"/>
-      <c r="DO31" s="50" t="n"/>
-      <c r="DP31" s="50" t="n"/>
-      <c r="DQ31" s="50" t="n"/>
-      <c r="DR31" s="50" t="n"/>
-      <c r="DS31" s="50" t="n"/>
-      <c r="DT31" s="50" t="n"/>
-      <c r="DU31" s="50" t="n"/>
-      <c r="DV31" s="50" t="n"/>
-      <c r="DW31" s="50" t="n"/>
-      <c r="DX31" s="50" t="n"/>
-      <c r="DY31" s="50" t="n"/>
-      <c r="DZ31" s="50" t="n"/>
-      <c r="EA31" s="50" t="n"/>
-      <c r="EB31" s="50" t="n"/>
-      <c r="EC31" s="50" t="n"/>
-      <c r="ED31" s="50" t="n"/>
-      <c r="EE31" s="50" t="n"/>
-      <c r="EF31" s="50" t="n"/>
-      <c r="EG31" s="50" t="n"/>
-      <c r="EH31" s="50" t="n"/>
-      <c r="EI31" s="50" t="n"/>
-      <c r="EJ31" s="50" t="n"/>
-      <c r="EK31" s="50" t="n"/>
-      <c r="EL31" s="50" t="n"/>
-      <c r="EM31" s="50" t="n"/>
-      <c r="EN31" s="50" t="n"/>
-      <c r="EO31" s="50" t="n"/>
-      <c r="EP31" s="50" t="n"/>
-      <c r="EQ31" s="50" t="n"/>
-      <c r="ER31" s="50" t="n"/>
-      <c r="ES31" s="50" t="n"/>
-      <c r="ET31" s="50" t="n"/>
-      <c r="EU31" s="50" t="n"/>
-      <c r="EV31" s="50" t="n"/>
-      <c r="EW31" s="50" t="n"/>
-      <c r="EX31" s="50" t="n"/>
-      <c r="EY31" s="50" t="n"/>
-      <c r="EZ31" s="50" t="n"/>
-      <c r="FA31" s="50" t="n"/>
-      <c r="FB31" s="50" t="n"/>
-      <c r="FC31" s="50" t="n"/>
-      <c r="FD31" s="50" t="n"/>
-      <c r="FE31" s="50" t="n"/>
-      <c r="FF31" s="50" t="n"/>
-      <c r="FG31" s="50" t="n"/>
-      <c r="FH31" s="50" t="n"/>
-      <c r="FI31" s="50" t="n"/>
-      <c r="FJ31" s="50" t="n"/>
-      <c r="FK31" s="50" t="n"/>
-      <c r="FL31" s="50" t="n"/>
-      <c r="FM31" s="50" t="n"/>
-      <c r="FN31" s="50" t="n"/>
-      <c r="FO31" s="50" t="n"/>
-      <c r="FP31" s="50" t="n"/>
-      <c r="FQ31" s="50" t="n"/>
-      <c r="FR31" s="50" t="n"/>
-      <c r="FS31" s="50" t="n"/>
-      <c r="FT31" s="50" t="n"/>
-      <c r="FU31" s="50" t="n"/>
-      <c r="FV31" s="50" t="n"/>
-      <c r="FW31" s="50" t="n"/>
-      <c r="FX31" s="50" t="n"/>
-      <c r="FY31" s="50" t="n"/>
-      <c r="FZ31" s="50" t="n"/>
-      <c r="GA31" s="50" t="n"/>
-      <c r="GB31" s="50" t="n"/>
-      <c r="GC31" s="50" t="n"/>
-      <c r="GD31" s="50" t="n"/>
-      <c r="GE31" s="50" t="n"/>
-      <c r="GF31" s="50" t="n"/>
-      <c r="GG31" s="50" t="n"/>
-      <c r="GH31" s="50" t="n"/>
-      <c r="GI31" s="50" t="n"/>
-      <c r="GJ31" s="50" t="n"/>
-      <c r="GK31" s="50" t="n"/>
-      <c r="GL31" s="50" t="n"/>
-      <c r="GM31" s="50" t="n"/>
-      <c r="GN31" s="50" t="n"/>
-      <c r="GO31" s="50" t="n"/>
-      <c r="GP31" s="50" t="n"/>
-      <c r="GQ31" s="50" t="n"/>
-      <c r="GR31" s="50" t="n"/>
-      <c r="GS31" s="50" t="n"/>
-      <c r="GT31" s="50" t="n"/>
-      <c r="GU31" s="50" t="n"/>
-      <c r="GV31" s="50" t="n"/>
-      <c r="GW31" s="50" t="n"/>
-      <c r="GX31" s="50" t="n"/>
-      <c r="GY31" s="50" t="n"/>
-      <c r="GZ31" s="50" t="n"/>
-      <c r="HA31" s="50" t="n"/>
-      <c r="HB31" s="50" t="n"/>
-      <c r="HC31" s="50" t="n"/>
-      <c r="HD31" s="50" t="n"/>
-      <c r="HE31" s="50" t="n"/>
-      <c r="HF31" s="50" t="n"/>
-      <c r="HG31" s="50" t="n"/>
-      <c r="HH31" s="50" t="n"/>
-      <c r="HI31" s="50" t="n"/>
-      <c r="HJ31" s="50" t="n"/>
-      <c r="HK31" s="50" t="n"/>
-      <c r="HL31" s="50" t="n"/>
-      <c r="HM31" s="50" t="n"/>
-      <c r="HN31" s="50" t="n"/>
-      <c r="HO31" s="50" t="n"/>
-      <c r="HP31" s="50" t="n"/>
-      <c r="HQ31" s="50" t="n"/>
-      <c r="HR31" s="50" t="n"/>
-      <c r="HS31" s="50" t="n"/>
-      <c r="HT31" s="50" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="K31" s="16" t="n"/>
+      <c r="L31" s="16" t="n"/>
+      <c r="M31" s="16" t="n"/>
+      <c r="AB31" s="16" t="n"/>
     </row>
     <row r="32" ht="32" customFormat="1" customHeight="1" s="23">
-      <c r="A32" s="16" t="n"/>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="25" t="n"/>
-      <c r="D32" s="42" t="n"/>
-      <c r="E32" s="88" t="n"/>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="16" t="n"/>
-      <c r="I32" s="16" t="n"/>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="18" t="n"/>
-      <c r="L32" s="18" t="n"/>
-      <c r="M32" s="18" t="n"/>
-      <c r="N32" s="16" t="n"/>
-      <c r="O32" s="16" t="n"/>
-      <c r="P32" s="16" t="n"/>
-      <c r="Q32" s="16" t="n"/>
-      <c r="R32" s="16" t="n"/>
-      <c r="S32" s="16" t="n"/>
-      <c r="T32" s="16" t="n"/>
-      <c r="U32" s="16" t="n"/>
-      <c r="V32" s="16" t="n"/>
-      <c r="W32" s="16" t="n"/>
-      <c r="X32" s="16" t="n"/>
-      <c r="Y32" s="16" t="n"/>
-      <c r="Z32" s="16" t="n"/>
-      <c r="AA32" s="16" t="n"/>
-      <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="16" t="n"/>
-      <c r="AD32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="K32" s="16" t="n"/>
+      <c r="L32" s="16" t="n"/>
+      <c r="M32" s="16" t="n"/>
+      <c r="AB32" s="16" t="n"/>
     </row>
     <row r="33" ht="74.5" customFormat="1" customHeight="1" s="51">
-      <c r="A33" s="60" t="n"/>
-      <c r="B33" s="61" t="n"/>
-      <c r="C33" s="61" t="n"/>
-      <c r="D33" s="61" t="n"/>
-      <c r="E33" s="61" t="n"/>
-      <c r="F33" s="61" t="n"/>
-      <c r="G33" s="61" t="n"/>
-      <c r="H33" s="61" t="n"/>
-      <c r="I33" s="61" t="n"/>
-      <c r="J33" s="61" t="n"/>
-      <c r="K33" s="61" t="n"/>
-      <c r="L33" s="61" t="n"/>
-      <c r="M33" s="61" t="n"/>
-      <c r="N33" s="61" t="n"/>
-      <c r="O33" s="61" t="n"/>
-      <c r="P33" s="61" t="n"/>
-      <c r="Q33" s="61" t="n"/>
-      <c r="R33" s="62" t="n"/>
-      <c r="S33" s="62" t="n"/>
-      <c r="T33" s="62" t="n"/>
-      <c r="U33" s="62" t="n"/>
-      <c r="V33" s="62" t="n"/>
-      <c r="W33" s="62" t="n"/>
-      <c r="X33" s="62" t="n"/>
-      <c r="Y33" s="61" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ 5P VIỆT NAM</t>
-        </is>
-      </c>
-      <c r="Z33" s="63" t="n"/>
-      <c r="AA33" s="63" t="n"/>
-      <c r="AB33" s="63" t="n"/>
-      <c r="AC33" s="55" t="n"/>
-      <c r="AD33" s="55" t="n"/>
-      <c r="AE33" s="50" t="n"/>
-      <c r="AF33" s="50" t="n"/>
-      <c r="AG33" s="50" t="n"/>
-      <c r="AH33" s="50" t="n"/>
-      <c r="AI33" s="50" t="n"/>
-      <c r="AJ33" s="50" t="n"/>
-      <c r="AK33" s="50" t="n"/>
-      <c r="AL33" s="50" t="n"/>
-      <c r="AM33" s="50" t="n"/>
-      <c r="AN33" s="50" t="n"/>
-      <c r="AO33" s="50" t="n"/>
-      <c r="AP33" s="50" t="n"/>
-      <c r="AQ33" s="50" t="n"/>
-      <c r="AR33" s="50" t="n"/>
-      <c r="AS33" s="50" t="n"/>
-      <c r="AT33" s="50" t="n"/>
-      <c r="AU33" s="50" t="n"/>
-      <c r="AV33" s="50" t="n"/>
-      <c r="AW33" s="50" t="n"/>
-      <c r="AX33" s="50" t="n"/>
-      <c r="AY33" s="50" t="n"/>
-      <c r="AZ33" s="50" t="n"/>
-      <c r="BA33" s="50" t="n"/>
-      <c r="BB33" s="50" t="n"/>
-      <c r="BC33" s="50" t="n"/>
-      <c r="BD33" s="50" t="n"/>
-      <c r="BE33" s="50" t="n"/>
-      <c r="BF33" s="50" t="n"/>
-      <c r="BG33" s="50" t="n"/>
-      <c r="BH33" s="50" t="n"/>
-      <c r="BI33" s="50" t="n"/>
-      <c r="BJ33" s="50" t="n"/>
-      <c r="BK33" s="50" t="n"/>
-      <c r="BL33" s="50" t="n"/>
-      <c r="BM33" s="50" t="n"/>
-      <c r="BN33" s="50" t="n"/>
-      <c r="BO33" s="50" t="n"/>
-      <c r="BP33" s="50" t="n"/>
-      <c r="BQ33" s="50" t="n"/>
-      <c r="BR33" s="50" t="n"/>
-      <c r="BS33" s="50" t="n"/>
-      <c r="BT33" s="50" t="n"/>
-      <c r="BU33" s="50" t="n"/>
-      <c r="BV33" s="50" t="n"/>
-      <c r="BW33" s="50" t="n"/>
-      <c r="BX33" s="50" t="n"/>
-      <c r="BY33" s="50" t="n"/>
-      <c r="BZ33" s="50" t="n"/>
-      <c r="CA33" s="50" t="n"/>
-      <c r="CB33" s="50" t="n"/>
-      <c r="CC33" s="50" t="n"/>
-      <c r="CD33" s="50" t="n"/>
-      <c r="CE33" s="50" t="n"/>
-      <c r="CF33" s="50" t="n"/>
-      <c r="CG33" s="50" t="n"/>
-      <c r="CH33" s="50" t="n"/>
-      <c r="CI33" s="50" t="n"/>
-      <c r="CJ33" s="50" t="n"/>
-      <c r="CK33" s="50" t="n"/>
-      <c r="CL33" s="50" t="n"/>
-      <c r="CM33" s="50" t="n"/>
-      <c r="CN33" s="50" t="n"/>
-      <c r="CO33" s="50" t="n"/>
-      <c r="CP33" s="50" t="n"/>
-      <c r="CQ33" s="50" t="n"/>
-      <c r="CR33" s="50" t="n"/>
-      <c r="CS33" s="50" t="n"/>
-      <c r="CT33" s="50" t="n"/>
-      <c r="CU33" s="50" t="n"/>
-      <c r="CV33" s="50" t="n"/>
-      <c r="CW33" s="50" t="n"/>
-      <c r="CX33" s="50" t="n"/>
-      <c r="CY33" s="50" t="n"/>
-      <c r="CZ33" s="50" t="n"/>
-      <c r="DA33" s="50" t="n"/>
-      <c r="DB33" s="50" t="n"/>
-      <c r="DC33" s="50" t="n"/>
-      <c r="DD33" s="50" t="n"/>
-      <c r="DE33" s="50" t="n"/>
-      <c r="DF33" s="50" t="n"/>
-      <c r="DG33" s="50" t="n"/>
-      <c r="DH33" s="50" t="n"/>
-      <c r="DI33" s="50" t="n"/>
-      <c r="DJ33" s="50" t="n"/>
-      <c r="DK33" s="50" t="n"/>
-      <c r="DL33" s="50" t="n"/>
-      <c r="DM33" s="50" t="n"/>
-      <c r="DN33" s="50" t="n"/>
-      <c r="DO33" s="50" t="n"/>
-      <c r="DP33" s="50" t="n"/>
-      <c r="DQ33" s="50" t="n"/>
-      <c r="DR33" s="50" t="n"/>
-      <c r="DS33" s="50" t="n"/>
-      <c r="DT33" s="50" t="n"/>
-      <c r="DU33" s="50" t="n"/>
-      <c r="DV33" s="50" t="n"/>
-      <c r="DW33" s="50" t="n"/>
-      <c r="DX33" s="50" t="n"/>
-      <c r="DY33" s="50" t="n"/>
-      <c r="DZ33" s="50" t="n"/>
-      <c r="EA33" s="50" t="n"/>
-      <c r="EB33" s="50" t="n"/>
-      <c r="EC33" s="50" t="n"/>
-      <c r="ED33" s="50" t="n"/>
-      <c r="EE33" s="50" t="n"/>
-      <c r="EF33" s="50" t="n"/>
-      <c r="EG33" s="50" t="n"/>
-      <c r="EH33" s="50" t="n"/>
-      <c r="EI33" s="50" t="n"/>
-      <c r="EJ33" s="50" t="n"/>
-      <c r="EK33" s="50" t="n"/>
-      <c r="EL33" s="50" t="n"/>
-      <c r="EM33" s="50" t="n"/>
-      <c r="EN33" s="50" t="n"/>
-      <c r="EO33" s="50" t="n"/>
-      <c r="EP33" s="50" t="n"/>
-      <c r="EQ33" s="50" t="n"/>
-      <c r="ER33" s="50" t="n"/>
-      <c r="ES33" s="50" t="n"/>
-      <c r="ET33" s="50" t="n"/>
-      <c r="EU33" s="50" t="n"/>
-      <c r="EV33" s="50" t="n"/>
-      <c r="EW33" s="50" t="n"/>
-      <c r="EX33" s="50" t="n"/>
-      <c r="EY33" s="50" t="n"/>
-      <c r="EZ33" s="50" t="n"/>
-      <c r="FA33" s="50" t="n"/>
-      <c r="FB33" s="50" t="n"/>
-      <c r="FC33" s="50" t="n"/>
-      <c r="FD33" s="50" t="n"/>
-      <c r="FE33" s="50" t="n"/>
-      <c r="FF33" s="50" t="n"/>
-      <c r="FG33" s="50" t="n"/>
-      <c r="FH33" s="50" t="n"/>
-      <c r="FI33" s="50" t="n"/>
-      <c r="FJ33" s="50" t="n"/>
-      <c r="FK33" s="50" t="n"/>
-      <c r="FL33" s="50" t="n"/>
-      <c r="FM33" s="50" t="n"/>
-      <c r="FN33" s="50" t="n"/>
-      <c r="FO33" s="50" t="n"/>
-      <c r="FP33" s="50" t="n"/>
-      <c r="FQ33" s="50" t="n"/>
-      <c r="FR33" s="50" t="n"/>
-      <c r="FS33" s="50" t="n"/>
-      <c r="FT33" s="50" t="n"/>
-      <c r="FU33" s="50" t="n"/>
-      <c r="FV33" s="50" t="n"/>
-      <c r="FW33" s="50" t="n"/>
-      <c r="FX33" s="50" t="n"/>
-      <c r="FY33" s="50" t="n"/>
-      <c r="FZ33" s="50" t="n"/>
-      <c r="GA33" s="50" t="n"/>
-      <c r="GB33" s="50" t="n"/>
-      <c r="GC33" s="50" t="n"/>
-      <c r="GD33" s="50" t="n"/>
-      <c r="GE33" s="50" t="n"/>
-      <c r="GF33" s="50" t="n"/>
-      <c r="GG33" s="50" t="n"/>
-      <c r="GH33" s="50" t="n"/>
-      <c r="GI33" s="50" t="n"/>
-      <c r="GJ33" s="50" t="n"/>
-      <c r="GK33" s="50" t="n"/>
-      <c r="GL33" s="50" t="n"/>
-      <c r="GM33" s="50" t="n"/>
-      <c r="GN33" s="50" t="n"/>
-      <c r="GO33" s="50" t="n"/>
-      <c r="GP33" s="50" t="n"/>
-      <c r="GQ33" s="50" t="n"/>
-      <c r="GR33" s="50" t="n"/>
-      <c r="GS33" s="50" t="n"/>
-      <c r="GT33" s="50" t="n"/>
-      <c r="GU33" s="50" t="n"/>
-      <c r="GV33" s="50" t="n"/>
-      <c r="GW33" s="50" t="n"/>
-      <c r="GX33" s="50" t="n"/>
-      <c r="GY33" s="50" t="n"/>
-      <c r="GZ33" s="50" t="n"/>
-      <c r="HA33" s="50" t="n"/>
-      <c r="HB33" s="50" t="n"/>
-      <c r="HC33" s="50" t="n"/>
-      <c r="HD33" s="50" t="n"/>
-      <c r="HE33" s="50" t="n"/>
-      <c r="HF33" s="50" t="n"/>
-      <c r="HG33" s="50" t="n"/>
-      <c r="HH33" s="50" t="n"/>
-      <c r="HI33" s="50" t="n"/>
-      <c r="HJ33" s="50" t="n"/>
-      <c r="HK33" s="50" t="n"/>
-      <c r="HL33" s="50" t="n"/>
-      <c r="HM33" s="50" t="n"/>
-      <c r="HN33" s="50" t="n"/>
-      <c r="HO33" s="50" t="n"/>
-      <c r="HP33" s="50" t="n"/>
-      <c r="HQ33" s="50" t="n"/>
-      <c r="HR33" s="50" t="n"/>
-      <c r="HS33" s="50" t="n"/>
-      <c r="HT33" s="50" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="K33" s="16" t="n"/>
+      <c r="L33" s="16" t="n"/>
+      <c r="M33" s="16" t="n"/>
+      <c r="AB33" s="16" t="n"/>
     </row>
     <row r="34" ht="85" customHeight="1">
-      <c r="A34" s="29" t="n"/>
-      <c r="B34" s="31" t="n"/>
-      <c r="C34" s="32" t="n"/>
-      <c r="D34" s="32" t="n"/>
-      <c r="E34" s="39" t="n"/>
-      <c r="F34" s="33" t="n"/>
-      <c r="G34" s="33" t="n"/>
-      <c r="H34" s="33" t="n"/>
-      <c r="I34" s="33" t="n"/>
-      <c r="J34" s="33" t="n"/>
-      <c r="K34" s="34" t="n"/>
-      <c r="L34" s="45" t="n"/>
-      <c r="M34" s="34" t="n"/>
-      <c r="N34" s="31" t="n"/>
-      <c r="O34" s="31" t="n"/>
-      <c r="P34" s="31" t="n"/>
-      <c r="Q34" s="31" t="n"/>
-      <c r="R34" s="31" t="n"/>
-      <c r="S34" s="31" t="n"/>
-      <c r="T34" s="35" t="n"/>
-      <c r="U34" s="31" t="n"/>
-      <c r="V34" s="31" t="n"/>
-      <c r="W34" s="31" t="n"/>
-      <c r="X34" s="31" t="n"/>
-      <c r="Y34" s="31" t="n"/>
-      <c r="Z34" s="31" t="n"/>
-      <c r="AA34" s="31" t="n"/>
-      <c r="AB34" s="31" t="n"/>
-      <c r="AC34" s="31" t="n"/>
-      <c r="AD34" s="36" t="n"/>
+      <c r="D34" s="42" t="n"/>
+      <c r="E34" s="88" t="n"/>
     </row>
     <row r="35" ht="52.5" customFormat="1" customHeight="1" s="31">
-      <c r="A35" s="29" t="n"/>
-      <c r="C35" s="37" t="n"/>
-      <c r="D35" s="37" t="n"/>
-      <c r="E35" s="30" t="n"/>
-      <c r="H35" s="33" t="n"/>
-      <c r="I35" s="33" t="n"/>
-      <c r="J35" s="33" t="n"/>
-      <c r="K35" s="38" t="n"/>
-      <c r="L35" s="38" t="n"/>
-      <c r="M35" s="44" t="n"/>
-      <c r="N35" s="33" t="n"/>
-      <c r="O35" s="33" t="n"/>
-      <c r="P35" s="33" t="n"/>
-      <c r="Q35" s="33" t="n"/>
-      <c r="R35" s="33" t="n"/>
-      <c r="S35" s="33" t="n"/>
-      <c r="T35" s="158" t="n"/>
-      <c r="U35" s="33" t="n"/>
-      <c r="AA35" s="35" t="n"/>
-      <c r="AB35" s="35" t="n"/>
-      <c r="AD35" s="36" t="n"/>
-      <c r="AE35" s="55" t="n"/>
+      <c r="D35" s="42" t="n"/>
+      <c r="E35" s="88" t="n"/>
     </row>
     <row r="36" ht="15" customFormat="1" customHeight="1" s="31">
-      <c r="C36" s="37" t="n"/>
-      <c r="D36" s="37" t="n"/>
-      <c r="E36" s="30" t="n"/>
-      <c r="K36" s="38" t="n"/>
-      <c r="L36" s="38" t="n"/>
-      <c r="M36" s="38" t="n"/>
-      <c r="N36" s="33" t="n"/>
-      <c r="O36" s="33" t="n"/>
-      <c r="P36" s="33" t="n"/>
-      <c r="Q36" s="33" t="n"/>
-      <c r="R36" s="33" t="n"/>
-      <c r="S36" s="33" t="n"/>
-      <c r="T36" s="33" t="n"/>
-      <c r="U36" s="33" t="n"/>
-      <c r="AA36" s="35" t="n"/>
-      <c r="AD36" s="36" t="n"/>
-      <c r="AE36" s="36" t="n"/>
+      <c r="D36" s="42" t="n"/>
+      <c r="E36" s="88" t="n"/>
     </row>
     <row r="37" ht="15" customFormat="1" customHeight="1" s="31">
-      <c r="C37" s="32" t="n"/>
-      <c r="D37" s="32" t="n"/>
-      <c r="E37" s="39" t="n"/>
-      <c r="F37" s="39" t="n"/>
-      <c r="G37" s="39" t="n"/>
-      <c r="K37" s="38" t="n"/>
-      <c r="L37" s="38" t="n"/>
-      <c r="M37" s="38" t="n"/>
-      <c r="N37" s="33" t="n"/>
-      <c r="O37" s="33" t="n"/>
-      <c r="P37" s="33" t="n"/>
-      <c r="Q37" s="33" t="n"/>
-      <c r="R37" s="33" t="n"/>
-      <c r="S37" s="33" t="n"/>
-      <c r="T37" s="33" t="n"/>
-      <c r="U37" s="33" t="n"/>
-      <c r="AD37" s="36" t="n"/>
-      <c r="AE37" s="36" t="n"/>
+      <c r="D37" s="42" t="n"/>
+      <c r="E37" s="88" t="n"/>
     </row>
     <row r="38" ht="15" customFormat="1" customHeight="1" s="31">
-      <c r="B38" s="33" t="n"/>
-      <c r="C38" s="33" t="n"/>
-      <c r="D38" s="33" t="n"/>
-      <c r="E38" s="39" t="n"/>
-      <c r="F38" s="33" t="n"/>
-      <c r="G38" s="33" t="n"/>
-      <c r="H38" s="33" t="n"/>
-      <c r="I38" s="33" t="n"/>
-      <c r="J38" s="33" t="n"/>
-      <c r="K38" s="33" t="n"/>
-      <c r="L38" s="33" t="n"/>
-      <c r="M38" s="33" t="n"/>
-      <c r="N38" s="33" t="n"/>
-      <c r="O38" s="33" t="n"/>
-      <c r="P38" s="33" t="n"/>
-      <c r="Q38" s="33" t="n"/>
-      <c r="T38" s="40" t="n"/>
-      <c r="W38" s="30" t="n"/>
-      <c r="X38" s="33" t="n"/>
-      <c r="Y38" s="33" t="n"/>
-      <c r="Z38" s="33" t="n"/>
-      <c r="AD38" s="36" t="n"/>
-      <c r="AE38" s="36" t="n"/>
+      <c r="D38" s="42" t="n"/>
+      <c r="E38" s="88" t="n"/>
     </row>
     <row r="39" ht="84.5" customFormat="1" customHeight="1" s="31">
-      <c r="A39" s="19" t="n"/>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="25" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="42" t="n"/>
-      <c r="F39" s="16" t="n"/>
-      <c r="G39" s="16" t="n"/>
-      <c r="H39" s="16" t="n"/>
-      <c r="I39" s="16" t="n"/>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="18" t="n"/>
-      <c r="L39" s="18" t="n"/>
-      <c r="M39" s="18" t="n"/>
-      <c r="N39" s="16" t="n"/>
-      <c r="O39" s="16" t="n"/>
-      <c r="P39" s="16" t="n"/>
-      <c r="Q39" s="16" t="n"/>
-      <c r="R39" s="16" t="n"/>
-      <c r="S39" s="16" t="n"/>
-      <c r="T39" s="16" t="n"/>
-      <c r="U39" s="16" t="n"/>
-      <c r="V39" s="16" t="n"/>
-      <c r="W39" s="16" t="n"/>
-      <c r="X39" s="16" t="n"/>
-      <c r="Y39" s="16" t="n"/>
-      <c r="Z39" s="16" t="n"/>
-      <c r="AA39" s="16" t="n"/>
-      <c r="AB39" s="16" t="n"/>
-      <c r="AC39" s="16" t="n"/>
-      <c r="AD39" s="20" t="n"/>
-      <c r="AE39" s="36" t="n"/>
+      <c r="D39" s="42" t="n"/>
+      <c r="E39" s="88" t="n"/>
     </row>
     <row r="40" customFormat="1" s="31">
-      <c r="A40" s="19" t="n"/>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="42" t="n"/>
-      <c r="F40" s="16" t="n"/>
-      <c r="G40" s="16" t="n"/>
-      <c r="H40" s="16" t="n"/>
-      <c r="I40" s="16" t="n"/>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
-      <c r="M40" s="16" t="n"/>
-      <c r="N40" s="16" t="n"/>
-      <c r="O40" s="16" t="n"/>
-      <c r="P40" s="16" t="n"/>
-      <c r="Q40" s="16" t="n"/>
-      <c r="R40" s="16" t="n"/>
-      <c r="S40" s="16" t="n"/>
-      <c r="T40" s="16" t="n"/>
-      <c r="U40" s="16" t="n"/>
-      <c r="V40" s="16" t="n"/>
-      <c r="W40" s="16" t="n"/>
-      <c r="X40" s="16" t="n"/>
-      <c r="Y40" s="16" t="n"/>
-      <c r="Z40" s="16" t="n"/>
-      <c r="AA40" s="16" t="n"/>
-      <c r="AB40" s="16" t="n"/>
-      <c r="AC40" s="16" t="n"/>
-      <c r="AD40" s="16" t="n"/>
-      <c r="AE40" s="41" t="n"/>
+      <c r="D40" s="42" t="n"/>
+      <c r="E40" s="88" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="42" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
-      <c r="M41" s="16" t="n"/>
-      <c r="AB41" s="16" t="n"/>
-      <c r="AE41" s="20" t="n"/>
+      <c r="D41" s="42" t="n"/>
+      <c r="E41" s="88" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="42" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
-      <c r="N42" s="18" t="n"/>
-      <c r="O42" s="18" t="n"/>
-      <c r="P42" s="18" t="n"/>
-      <c r="Q42" s="18" t="n"/>
-      <c r="R42" s="18" t="n"/>
-      <c r="S42" s="18" t="n"/>
-      <c r="T42" s="18" t="n"/>
-      <c r="U42" s="18" t="n"/>
-      <c r="V42" s="18" t="n"/>
-      <c r="W42" s="18" t="n"/>
-      <c r="X42" s="18" t="n"/>
-      <c r="Y42" s="18" t="n"/>
-      <c r="Z42" s="18" t="n"/>
-      <c r="AA42" s="18" t="n"/>
-      <c r="AB42" s="18" t="n"/>
-      <c r="AC42" s="18" t="n"/>
-      <c r="AD42" s="18" t="n"/>
+      <c r="D42" s="42" t="n"/>
+      <c r="E42" s="88" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="42" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="16" t="n"/>
-      <c r="N43" s="18" t="n"/>
-      <c r="O43" s="18" t="n"/>
-      <c r="P43" s="18" t="n"/>
-      <c r="Q43" s="18" t="n"/>
-      <c r="R43" s="18" t="n"/>
-      <c r="S43" s="18" t="n"/>
-      <c r="T43" s="18" t="n"/>
-      <c r="U43" s="18" t="n"/>
-      <c r="V43" s="18" t="n"/>
-      <c r="W43" s="18" t="n"/>
-      <c r="X43" s="18" t="n"/>
-      <c r="Y43" s="18" t="n"/>
-      <c r="Z43" s="18" t="n"/>
-      <c r="AA43" s="18" t="n"/>
-      <c r="AB43" s="18" t="n"/>
-      <c r="AC43" s="18" t="n"/>
-      <c r="AD43" s="18" t="n"/>
+      <c r="D43" s="42" t="n"/>
+      <c r="E43" s="88" t="n"/>
     </row>
     <row r="44" customFormat="1" s="18">
-      <c r="A44" s="88" t="n"/>
-      <c r="G44" s="16" t="n"/>
-      <c r="H44" s="16" t="n"/>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="16" t="n"/>
-      <c r="M44" s="16" t="n"/>
-      <c r="N44" s="16" t="n"/>
-      <c r="O44" s="16" t="n"/>
-      <c r="P44" s="16" t="n"/>
-      <c r="Q44" s="16" t="n"/>
-      <c r="R44" s="16" t="n"/>
-      <c r="S44" s="16" t="n"/>
-      <c r="T44" s="16" t="n"/>
-      <c r="U44" s="16" t="n"/>
-      <c r="V44" s="16" t="n"/>
-      <c r="W44" s="16" t="n"/>
-      <c r="X44" s="16" t="n"/>
-      <c r="Y44" s="16" t="n"/>
-      <c r="Z44" s="16" t="n"/>
-      <c r="AA44" s="16" t="n"/>
-      <c r="AB44" s="16" t="n"/>
-      <c r="AC44" s="16" t="n"/>
-      <c r="AD44" s="16" t="n"/>
+      <c r="D44" s="42" t="n"/>
+      <c r="E44" s="88" t="n"/>
     </row>
     <row r="45" customFormat="1" s="18">
-      <c r="A45" s="16" t="n"/>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
       <c r="D45" s="42" t="n"/>
       <c r="E45" s="88" t="n"/>
-      <c r="F45" s="16" t="n"/>
-      <c r="G45" s="16" t="n"/>
-      <c r="H45" s="16" t="n"/>
-      <c r="I45" s="16" t="n"/>
-      <c r="J45" s="16" t="n"/>
-      <c r="K45" s="16" t="n"/>
-      <c r="L45" s="16" t="n"/>
-      <c r="M45" s="16" t="n"/>
-      <c r="N45" s="16" t="n"/>
-      <c r="O45" s="16" t="n"/>
-      <c r="P45" s="16" t="n"/>
-      <c r="Q45" s="16" t="n"/>
-      <c r="R45" s="16" t="n"/>
-      <c r="S45" s="16" t="n"/>
-      <c r="T45" s="16" t="n"/>
-      <c r="U45" s="16" t="n"/>
-      <c r="V45" s="16" t="n"/>
-      <c r="W45" s="16" t="n"/>
-      <c r="X45" s="16" t="n"/>
-      <c r="Y45" s="16" t="n"/>
-      <c r="Z45" s="16" t="n"/>
-      <c r="AA45" s="16" t="n"/>
-      <c r="AB45" s="16" t="n"/>
-      <c r="AC45" s="16" t="n"/>
-      <c r="AD45" s="16" t="n"/>
     </row>
     <row r="46">
-      <c r="C46" s="16" t="n"/>
-      <c r="K46" s="16" t="n"/>
-      <c r="L46" s="16" t="n"/>
-      <c r="M46" s="16" t="n"/>
-      <c r="AB46" s="16" t="n"/>
+      <c r="D46" s="42" t="n"/>
+      <c r="E46" s="88" t="n"/>
     </row>
     <row r="47">
-      <c r="C47" s="16" t="n"/>
-      <c r="K47" s="16" t="n"/>
-      <c r="L47" s="16" t="n"/>
-      <c r="M47" s="16" t="n"/>
-      <c r="AB47" s="16" t="n"/>
+      <c r="D47" s="42" t="n"/>
+      <c r="E47" s="88" t="n"/>
     </row>
     <row r="48">
-      <c r="C48" s="16" t="n"/>
-      <c r="K48" s="16" t="n"/>
-      <c r="L48" s="16" t="n"/>
-      <c r="M48" s="16" t="n"/>
-      <c r="AB48" s="16" t="n"/>
+      <c r="D48" s="42" t="n"/>
+      <c r="E48" s="88" t="n"/>
     </row>
     <row r="49" customFormat="1" s="16">
       <c r="D49" s="42" t="n"/>
@@ -4628,66 +3967,21 @@
       <c r="D188" s="42" t="n"/>
       <c r="E188" s="88" t="n"/>
     </row>
-    <row r="189" customFormat="1" s="16">
-      <c r="D189" s="42" t="n"/>
-      <c r="E189" s="88" t="n"/>
-    </row>
-    <row r="190" customFormat="1" s="16">
-      <c r="D190" s="42" t="n"/>
-      <c r="E190" s="88" t="n"/>
-    </row>
-    <row r="191" customFormat="1" s="16">
-      <c r="D191" s="42" t="n"/>
-      <c r="E191" s="88" t="n"/>
-    </row>
-    <row r="192" customFormat="1" s="16">
-      <c r="D192" s="42" t="n"/>
-      <c r="E192" s="88" t="n"/>
-    </row>
-    <row r="193" customFormat="1" s="16">
-      <c r="D193" s="42" t="n"/>
-      <c r="E193" s="88" t="n"/>
-    </row>
-    <row r="194" customFormat="1" s="16">
-      <c r="D194" s="42" t="n"/>
-      <c r="E194" s="88" t="n"/>
-    </row>
-    <row r="195" customFormat="1" s="16">
-      <c r="D195" s="42" t="n"/>
-      <c r="E195" s="88" t="n"/>
-    </row>
-    <row r="196" customFormat="1" s="16">
-      <c r="D196" s="42" t="n"/>
-      <c r="E196" s="88" t="n"/>
-    </row>
-    <row r="197" customFormat="1" s="16">
-      <c r="D197" s="42" t="n"/>
-      <c r="E197" s="88" t="n"/>
-    </row>
-    <row r="198" customFormat="1" s="16">
-      <c r="D198" s="42" t="n"/>
-      <c r="E198" s="88" t="n"/>
-    </row>
-    <row r="199" customFormat="1" s="16">
-      <c r="D199" s="42" t="n"/>
-      <c r="E199" s="88" t="n"/>
-    </row>
-    <row r="200" customFormat="1" s="16">
-      <c r="D200" s="42" t="n"/>
-      <c r="E200" s="88" t="n"/>
-    </row>
-    <row r="201" customFormat="1" s="16">
-      <c r="D201" s="42" t="n"/>
-      <c r="E201" s="88" t="n"/>
-    </row>
-    <row r="202" customFormat="1" s="16">
-      <c r="D202" s="42" t="n"/>
-      <c r="E202" s="88" t="n"/>
-    </row>
-    <row r="203" customFormat="1" s="16">
-      <c r="D203" s="42" t="n"/>
-      <c r="E203" s="88" t="n"/>
-    </row>
+    <row r="189" customFormat="1" s="16"/>
+    <row r="190" customFormat="1" s="16"/>
+    <row r="191" customFormat="1" s="16"/>
+    <row r="192" customFormat="1" s="16"/>
+    <row r="193" customFormat="1" s="16"/>
+    <row r="194" customFormat="1" s="16"/>
+    <row r="195" customFormat="1" s="16"/>
+    <row r="196" customFormat="1" s="16"/>
+    <row r="197" customFormat="1" s="16"/>
+    <row r="198" customFormat="1" s="16"/>
+    <row r="199" customFormat="1" s="16"/>
+    <row r="200" customFormat="1" s="16"/>
+    <row r="201" customFormat="1" s="16"/>
+    <row r="202" customFormat="1" s="16"/>
+    <row r="203" customFormat="1" s="16"/>
   </sheetData>
   <autoFilter ref="A12:II33">
     <filterColumn colId="28" hiddenButton="0" showButton="0"/>
